--- a/research/traditional_assets/database/data/canada/canada_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_semiconductor.xlsx
@@ -1513,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1650,22 +1650,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1174892188913704</v>
+        <v>0.1172109474613083</v>
       </c>
       <c r="C2">
-        <v>4975.956168483648</v>
+        <v>4926.578012445198</v>
       </c>
       <c r="D2">
-        <v>2807.156168483647</v>
+        <v>2818.09498653861</v>
       </c>
       <c r="E2">
-        <v>-5295.997409341193</v>
+        <v>-5235.680435247781</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>60.31697409341193</v>
       </c>
       <c r="G2">
         <v>2168.8</v>
@@ -1686,28 +1686,28 @@
         <v>476</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.03394379689862</v>
       </c>
       <c r="N2">
-        <v>476</v>
+        <v>472.9660562031014</v>
       </c>
       <c r="O2">
-        <v>126.14</v>
+        <v>125.3360048938219</v>
       </c>
       <c r="P2">
-        <v>349.86</v>
+        <v>347.6300513092795</v>
       </c>
       <c r="Q2">
-        <v>714.86</v>
+        <v>712.6300513092795</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1174892188913704</v>
+        <v>0.1180214570316245</v>
       </c>
       <c r="T2">
-        <v>1.655640159154052</v>
+        <v>1.667932033062923</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>156.891502237642</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1732,22 +1732,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1172109474613083</v>
+        <v>0.1169326760312462</v>
       </c>
       <c r="C3">
-        <v>4926.578012445198</v>
+        <v>4877.285441842673</v>
       </c>
       <c r="D3">
-        <v>2818.09498653861</v>
+        <v>2829.119390029497</v>
       </c>
       <c r="E3">
-        <v>-5235.680435247781</v>
+        <v>-5175.363461154369</v>
       </c>
       <c r="F3">
-        <v>60.31697409341193</v>
+        <v>120.6339481868239</v>
       </c>
       <c r="G3">
         <v>2168.8</v>
@@ -1768,28 +1768,28 @@
         <v>476</v>
       </c>
       <c r="M3">
-        <v>3.03394379689862</v>
+        <v>6.06788759379724</v>
       </c>
       <c r="N3">
-        <v>472.9660562031014</v>
+        <v>469.9321124062027</v>
       </c>
       <c r="O3">
-        <v>125.3360048938219</v>
+        <v>124.5320097876437</v>
       </c>
       <c r="P3">
-        <v>347.6300513092795</v>
+        <v>345.400102618559</v>
       </c>
       <c r="Q3">
-        <v>712.6300513092795</v>
+        <v>710.400102618559</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1180214570316245</v>
+        <v>0.118564557174741</v>
       </c>
       <c r="T3">
-        <v>1.667932033062923</v>
+        <v>1.680474761541362</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>156.891502237642</v>
+        <v>78.44575111882102</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1814,22 +1814,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1169326760312462</v>
+        <v>0.1166544046011841</v>
       </c>
       <c r="C4">
-        <v>4877.285441842673</v>
+        <v>4828.079465052975</v>
       </c>
       <c r="D4">
-        <v>2829.119390029497</v>
+        <v>2840.23038733321</v>
       </c>
       <c r="E4">
-        <v>-5175.363461154369</v>
+        <v>-5115.046487060958</v>
       </c>
       <c r="F4">
-        <v>120.6339481868239</v>
+        <v>180.9509222802358</v>
       </c>
       <c r="G4">
         <v>2168.8</v>
@@ -1850,28 +1850,28 @@
         <v>476</v>
       </c>
       <c r="M4">
-        <v>6.06788759379724</v>
+        <v>9.101831390695859</v>
       </c>
       <c r="N4">
-        <v>469.9321124062027</v>
+        <v>466.8981686093042</v>
       </c>
       <c r="O4">
-        <v>124.5320097876437</v>
+        <v>123.7280146814656</v>
       </c>
       <c r="P4">
-        <v>345.400102618559</v>
+        <v>343.1701539278386</v>
       </c>
       <c r="Q4">
-        <v>710.400102618559</v>
+        <v>708.1701539278386</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.118564557174741</v>
+        <v>0.1191188552589526</v>
       </c>
       <c r="T4">
-        <v>1.680474761541362</v>
+        <v>1.693276102978121</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>78.44575111882102</v>
+        <v>52.29716741254735</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1896,22 +1896,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1166544046011841</v>
+        <v>0.1163761331711219</v>
       </c>
       <c r="C5">
-        <v>4828.079465052975</v>
+        <v>4778.961106356538</v>
       </c>
       <c r="D5">
-        <v>2840.23038733321</v>
+        <v>2851.429002730186</v>
       </c>
       <c r="E5">
-        <v>-5115.046487060958</v>
+        <v>-5054.729512967545</v>
       </c>
       <c r="F5">
-        <v>180.9509222802358</v>
+        <v>241.2678963736477</v>
       </c>
       <c r="G5">
         <v>2168.8</v>
@@ -1932,28 +1932,28 @@
         <v>476</v>
       </c>
       <c r="M5">
-        <v>9.101831390695859</v>
+        <v>12.13577518759448</v>
       </c>
       <c r="N5">
-        <v>466.8981686093042</v>
+        <v>463.8642248124055</v>
       </c>
       <c r="O5">
-        <v>123.7280146814656</v>
+        <v>122.9240195752875</v>
       </c>
       <c r="P5">
-        <v>343.1701539278386</v>
+        <v>340.9402052371181</v>
       </c>
       <c r="Q5">
-        <v>708.1701539278386</v>
+        <v>705.9402052371181</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1191188552589526</v>
+        <v>0.1196847012199186</v>
       </c>
       <c r="T5">
-        <v>1.693276102978121</v>
+        <v>1.706344139028144</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.29716741254735</v>
+        <v>39.22287555941051</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1978,22 +1978,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1163761331711219</v>
+        <v>0.1160978617410598</v>
       </c>
       <c r="C6">
-        <v>4778.961106356538</v>
+        <v>4729.9314062521</v>
       </c>
       <c r="D6">
-        <v>2851.429002730186</v>
+        <v>2862.71627671916</v>
       </c>
       <c r="E6">
-        <v>-5054.729512967545</v>
+        <v>-4994.412538874133</v>
       </c>
       <c r="F6">
-        <v>241.2678963736477</v>
+        <v>301.5848704670597</v>
       </c>
       <c r="G6">
         <v>2168.8</v>
@@ -2014,28 +2014,28 @@
         <v>476</v>
       </c>
       <c r="M6">
-        <v>12.13577518759448</v>
+        <v>15.1697189844931</v>
       </c>
       <c r="N6">
-        <v>463.8642248124055</v>
+        <v>460.8302810155069</v>
       </c>
       <c r="O6">
-        <v>122.9240195752875</v>
+        <v>122.1200244691093</v>
       </c>
       <c r="P6">
-        <v>340.9402052371181</v>
+        <v>338.7102565463975</v>
       </c>
       <c r="Q6">
-        <v>705.9402052371181</v>
+        <v>703.7102565463975</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1196847012199186</v>
+        <v>0.1202624597274314</v>
       </c>
       <c r="T6">
-        <v>1.706344139028144</v>
+        <v>1.71968729162659</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.22287555941051</v>
+        <v>31.37830044752841</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2060,22 +2060,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1160978617410598</v>
+        <v>0.1158195903109976</v>
       </c>
       <c r="C7">
-        <v>4729.9314062521</v>
+        <v>4680.991421778974</v>
       </c>
       <c r="D7">
-        <v>2862.71627671916</v>
+        <v>2874.093266339445</v>
       </c>
       <c r="E7">
-        <v>-4994.412538874133</v>
+        <v>-4934.095564780721</v>
       </c>
       <c r="F7">
-        <v>301.5848704670597</v>
+        <v>361.9018445604716</v>
       </c>
       <c r="G7">
         <v>2168.8</v>
@@ -2096,28 +2096,28 @@
         <v>476</v>
       </c>
       <c r="M7">
-        <v>15.1697189844931</v>
+        <v>18.20366278139172</v>
       </c>
       <c r="N7">
-        <v>460.8302810155069</v>
+        <v>457.7963372186083</v>
       </c>
       <c r="O7">
-        <v>122.1200244691093</v>
+        <v>121.3160293629312</v>
       </c>
       <c r="P7">
-        <v>338.7102565463975</v>
+        <v>336.4803078556771</v>
       </c>
       <c r="Q7">
-        <v>703.7102565463975</v>
+        <v>701.4803078556771</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1202624597274314</v>
+        <v>0.1208525109691464</v>
       </c>
       <c r="T7">
-        <v>1.71968729162659</v>
+        <v>1.733314341088832</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.37830044752841</v>
+        <v>26.14858370627367</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2142,22 +2142,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1158195903109976</v>
+        <v>0.1155413188809355</v>
       </c>
       <c r="C8">
-        <v>4680.991421778974</v>
+        <v>4632.142226847031</v>
       </c>
       <c r="D8">
-        <v>2874.093266339445</v>
+        <v>2885.561045500914</v>
       </c>
       <c r="E8">
-        <v>-4934.095564780721</v>
+        <v>-4873.77859068731</v>
       </c>
       <c r="F8">
-        <v>361.9018445604715</v>
+        <v>422.2188186538834</v>
       </c>
       <c r="G8">
         <v>2168.8</v>
@@ -2178,28 +2178,28 @@
         <v>476</v>
       </c>
       <c r="M8">
-        <v>18.20366278139172</v>
+        <v>21.23760657829034</v>
       </c>
       <c r="N8">
-        <v>457.7963372186083</v>
+        <v>454.7623934217096</v>
       </c>
       <c r="O8">
-        <v>121.3160293629312</v>
+        <v>120.5120342567531</v>
       </c>
       <c r="P8">
-        <v>336.4803078556771</v>
+        <v>334.2503591649566</v>
       </c>
       <c r="Q8">
-        <v>701.4803078556771</v>
+        <v>699.2503591649565</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1208525109691464</v>
+        <v>0.1214552514848769</v>
       </c>
       <c r="T8">
-        <v>1.733314341088832</v>
+        <v>1.74723444537822</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.14858370627368</v>
+        <v>22.41307174823458</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2224,22 +2224,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1155413188809355</v>
+        <v>0.1152630474508734</v>
       </c>
       <c r="C9">
-        <v>4632.142226847031</v>
+        <v>4583.384912574635</v>
       </c>
       <c r="D9">
-        <v>2885.561045500915</v>
+        <v>2897.12070532193</v>
       </c>
       <c r="E9">
-        <v>-4873.77859068731</v>
+        <v>-4813.461616593898</v>
       </c>
       <c r="F9">
-        <v>422.2188186538835</v>
+        <v>482.5357927472954</v>
       </c>
       <c r="G9">
         <v>2168.8</v>
@@ -2260,28 +2260,28 @@
         <v>476</v>
       </c>
       <c r="M9">
-        <v>21.23760657829034</v>
+        <v>24.27155037518896</v>
       </c>
       <c r="N9">
-        <v>454.7623934217096</v>
+        <v>451.728449624811</v>
       </c>
       <c r="O9">
-        <v>120.5120342567531</v>
+        <v>119.7080391505749</v>
       </c>
       <c r="P9">
-        <v>334.2503591649566</v>
+        <v>332.0204104742361</v>
       </c>
       <c r="Q9">
-        <v>699.2503591649565</v>
+        <v>697.0204104742361</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1214552514848769</v>
+        <v>0.1220710950552971</v>
       </c>
       <c r="T9">
-        <v>1.74723444537822</v>
+        <v>1.761457160630419</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.41307174823458</v>
+        <v>19.61143777970526</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2306,22 +2306,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1152630474508734</v>
+        <v>0.1149847760208113</v>
       </c>
       <c r="C10">
-        <v>4583.384912574635</v>
+        <v>4534.720587634702</v>
       </c>
       <c r="D10">
-        <v>2897.12070532193</v>
+        <v>2908.773354475408</v>
       </c>
       <c r="E10">
-        <v>-4813.461616593898</v>
+        <v>-4753.144642500485</v>
       </c>
       <c r="F10">
-        <v>482.5357927472954</v>
+        <v>542.8527668407073</v>
       </c>
       <c r="G10">
         <v>2168.8</v>
@@ -2342,28 +2342,28 @@
         <v>476</v>
       </c>
       <c r="M10">
-        <v>24.27155037518896</v>
+        <v>27.30549417208758</v>
       </c>
       <c r="N10">
-        <v>451.728449624811</v>
+        <v>448.6945058279124</v>
       </c>
       <c r="O10">
-        <v>119.7080391505749</v>
+        <v>118.9040440443968</v>
       </c>
       <c r="P10">
-        <v>332.0204104742361</v>
+        <v>329.7904617835156</v>
       </c>
       <c r="Q10">
-        <v>697.0204104742361</v>
+        <v>694.7904617835156</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1220710950552971</v>
+        <v>0.1227004736492431</v>
       </c>
       <c r="T10">
-        <v>1.761457160630419</v>
+        <v>1.775992463031019</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.61143777970526</v>
+        <v>17.43238913751578</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2388,22 +2388,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1149847760208113</v>
+        <v>0.1147065045907491</v>
       </c>
       <c r="C11">
-        <v>4534.720587634702</v>
+        <v>4486.150378609173</v>
       </c>
       <c r="D11">
-        <v>2908.773354475408</v>
+        <v>2920.520119543291</v>
       </c>
       <c r="E11">
-        <v>-4753.144642500485</v>
+        <v>-4692.827668407073</v>
       </c>
       <c r="F11">
-        <v>542.8527668407073</v>
+        <v>603.1697409341192</v>
       </c>
       <c r="G11">
         <v>2168.8</v>
@@ -2424,28 +2424,28 @@
         <v>476</v>
       </c>
       <c r="M11">
-        <v>27.30549417208758</v>
+        <v>30.33943796898619</v>
       </c>
       <c r="N11">
-        <v>448.6945058279124</v>
+        <v>445.6605620310138</v>
       </c>
       <c r="O11">
-        <v>118.9040440443968</v>
+        <v>118.1000489382187</v>
       </c>
       <c r="P11">
-        <v>329.7904617835156</v>
+        <v>327.5605130927951</v>
       </c>
       <c r="Q11">
-        <v>694.7904617835156</v>
+        <v>692.5605130927952</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1227004736492431</v>
+        <v>0.1233438384341657</v>
       </c>
       <c r="T11">
-        <v>1.775992463031019</v>
+        <v>1.790850772151632</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.43238913751578</v>
+        <v>15.68915022376421</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2470,22 +2470,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1147065045907491</v>
+        <v>0.114428233160687</v>
       </c>
       <c r="C12">
-        <v>4486.150378609173</v>
+        <v>4437.675430352089</v>
       </c>
       <c r="D12">
-        <v>2920.520119543291</v>
+        <v>2932.36214537962</v>
       </c>
       <c r="E12">
-        <v>-4692.827668407073</v>
+        <v>-4632.510694313662</v>
       </c>
       <c r="F12">
-        <v>603.1697409341193</v>
+        <v>663.4867150275312</v>
       </c>
       <c r="G12">
         <v>2168.8</v>
@@ -2506,28 +2506,28 @@
         <v>476</v>
       </c>
       <c r="M12">
-        <v>30.3394379689862</v>
+        <v>33.37338176588482</v>
       </c>
       <c r="N12">
-        <v>445.6605620310138</v>
+        <v>442.6266182341152</v>
       </c>
       <c r="O12">
-        <v>118.1000489382187</v>
+        <v>117.2960538320405</v>
       </c>
       <c r="P12">
-        <v>327.5605130927951</v>
+        <v>325.3305644020747</v>
       </c>
       <c r="Q12">
-        <v>692.5605130927952</v>
+        <v>690.3305644020747</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1233438384341657</v>
+        <v>0.1240016608547045</v>
       </c>
       <c r="T12">
-        <v>1.790850772151632</v>
+        <v>1.806042975859226</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.6891502237642</v>
+        <v>14.26286383978564</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2552,22 +2552,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.114428233160687</v>
+        <v>0.1141499617306249</v>
       </c>
       <c r="C13">
-        <v>4437.675430352089</v>
+        <v>4389.296906361558</v>
       </c>
       <c r="D13">
-        <v>2932.36214537962</v>
+        <v>2944.300595482501</v>
       </c>
       <c r="E13">
-        <v>-4632.510694313662</v>
+        <v>-4572.19372022025</v>
       </c>
       <c r="F13">
-        <v>663.4867150275312</v>
+        <v>723.8036891209431</v>
       </c>
       <c r="G13">
         <v>2168.8</v>
@@ -2588,28 +2588,28 @@
         <v>476</v>
       </c>
       <c r="M13">
-        <v>33.37338176588482</v>
+        <v>36.40732556278343</v>
       </c>
       <c r="N13">
-        <v>442.6266182341152</v>
+        <v>439.5926744372165</v>
       </c>
       <c r="O13">
-        <v>117.2960538320405</v>
+        <v>116.4920587258624</v>
       </c>
       <c r="P13">
-        <v>325.3305644020747</v>
+        <v>323.1006157113542</v>
       </c>
       <c r="Q13">
-        <v>690.3305644020747</v>
+        <v>688.1006157113542</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1240016608547045</v>
+        <v>0.124674433784801</v>
       </c>
       <c r="T13">
-        <v>1.806042975859226</v>
+        <v>1.82158045692381</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.26286383978564</v>
+        <v>13.07429185313684</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2634,22 +2634,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1141499617306249</v>
+        <v>0.1140150153005627</v>
       </c>
       <c r="C14">
-        <v>4389.296906361558</v>
+        <v>4334.804498203367</v>
       </c>
       <c r="D14">
-        <v>2944.300595482501</v>
+        <v>2950.125161417722</v>
       </c>
       <c r="E14">
-        <v>-4572.19372022025</v>
+        <v>-4511.876746126838</v>
       </c>
       <c r="F14">
-        <v>723.8036891209431</v>
+        <v>784.1206632143551</v>
       </c>
       <c r="G14">
         <v>2168.8</v>
@@ -2670,45 +2670,45 @@
         <v>476</v>
       </c>
       <c r="M14">
-        <v>36.40732556278343</v>
+        <v>40.6174503545036</v>
       </c>
       <c r="N14">
-        <v>439.5926744372165</v>
+        <v>435.3825496454964</v>
       </c>
       <c r="O14">
-        <v>116.4920587258624</v>
+        <v>115.3763756560566</v>
       </c>
       <c r="P14">
-        <v>323.1006157113542</v>
+        <v>320.0061739894398</v>
       </c>
       <c r="Q14">
-        <v>688.1006157113542</v>
+        <v>685.0061739894398</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.124674433784801</v>
+        <v>0.1253626727592675</v>
       </c>
       <c r="T14">
-        <v>1.82158045692381</v>
+        <v>1.837475121461143</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.265</v>
       </c>
       <c r="W14">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.07429185313684</v>
+        <v>11.71910092449271</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2716,22 +2716,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1140150153005627</v>
+        <v>0.1137477688705006</v>
       </c>
       <c r="C15">
-        <v>4334.804498203367</v>
+        <v>4286.090707418709</v>
       </c>
       <c r="D15">
-        <v>2950.125161417722</v>
+        <v>2961.728344726476</v>
       </c>
       <c r="E15">
-        <v>-4511.876746126838</v>
+        <v>-4451.559772033426</v>
       </c>
       <c r="F15">
-        <v>784.1206632143551</v>
+        <v>844.4376373077671</v>
       </c>
       <c r="G15">
         <v>2168.8</v>
@@ -2752,28 +2752,28 @@
         <v>476</v>
       </c>
       <c r="M15">
-        <v>40.6174503545036</v>
+        <v>43.74186961254233</v>
       </c>
       <c r="N15">
-        <v>435.3825496454964</v>
+        <v>432.2581303874576</v>
       </c>
       <c r="O15">
-        <v>115.3763756560566</v>
+        <v>114.5484045526763</v>
       </c>
       <c r="P15">
-        <v>320.0061739894398</v>
+        <v>317.7097258347814</v>
       </c>
       <c r="Q15">
-        <v>685.0061739894398</v>
+        <v>682.7097258347814</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1253626727592675</v>
+        <v>0.1260669172912798</v>
       </c>
       <c r="T15">
-        <v>1.837475121461143</v>
+        <v>1.85373942935981</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.71910092449271</v>
+        <v>10.88202228702895</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2798,22 +2798,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1137477688705006</v>
+        <v>0.1134805224404385</v>
       </c>
       <c r="C16">
-        <v>4286.090707418709</v>
+        <v>4237.468550362778</v>
       </c>
       <c r="D16">
-        <v>2961.728344726476</v>
+        <v>2973.423161763957</v>
       </c>
       <c r="E16">
-        <v>-4451.559772033426</v>
+        <v>-4391.242797940014</v>
       </c>
       <c r="F16">
-        <v>844.4376373077671</v>
+        <v>904.7546114011791</v>
       </c>
       <c r="G16">
         <v>2168.8</v>
@@ -2834,28 +2834,28 @@
         <v>476</v>
       </c>
       <c r="M16">
-        <v>43.74186961254233</v>
+        <v>46.86628887058107</v>
       </c>
       <c r="N16">
-        <v>432.2581303874576</v>
+        <v>429.1337111294189</v>
       </c>
       <c r="O16">
-        <v>114.5484045526763</v>
+        <v>113.720433449296</v>
       </c>
       <c r="P16">
-        <v>317.7097258347814</v>
+        <v>315.4132776801229</v>
       </c>
       <c r="Q16">
-        <v>682.7097258347814</v>
+        <v>680.413277680123</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1260669172912798</v>
+        <v>0.1267877322828688</v>
       </c>
       <c r="T16">
-        <v>1.85373942935981</v>
+        <v>1.870386426856092</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.88202228702895</v>
+        <v>10.15655413456035</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2880,22 +2880,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1134805224404385</v>
+        <v>0.1134131960103763</v>
       </c>
       <c r="C17">
-        <v>4237.468550362779</v>
+        <v>4180.11238833503</v>
       </c>
       <c r="D17">
-        <v>2973.423161763957</v>
+        <v>2976.383973829621</v>
       </c>
       <c r="E17">
-        <v>-4391.242797940014</v>
+        <v>-4330.925823846602</v>
       </c>
       <c r="F17">
-        <v>904.7546114011789</v>
+        <v>965.0715854945909</v>
       </c>
       <c r="G17">
         <v>2168.8</v>
@@ -2916,45 +2916,45 @@
         <v>476</v>
       </c>
       <c r="M17">
-        <v>46.86628887058107</v>
+        <v>51.63132982396061</v>
       </c>
       <c r="N17">
-        <v>429.1337111294189</v>
+        <v>424.3686701760394</v>
       </c>
       <c r="O17">
-        <v>113.720433449296</v>
+        <v>112.4576975966504</v>
       </c>
       <c r="P17">
-        <v>315.4132776801229</v>
+        <v>311.910972579389</v>
       </c>
       <c r="Q17">
-        <v>680.413277680123</v>
+        <v>676.910972579389</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1267877322828688</v>
+        <v>0.1275257095361623</v>
       </c>
       <c r="T17">
-        <v>1.870386426856092</v>
+        <v>1.887429781435619</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.265</v>
       </c>
       <c r="W17">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.15655413456035</v>
+        <v>9.219208601113777</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2962,22 +2962,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1134131960103763</v>
+        <v>0.1131584445803142</v>
       </c>
       <c r="C18">
-        <v>4180.11238833503</v>
+        <v>4131.052177643317</v>
       </c>
       <c r="D18">
-        <v>2976.383973829621</v>
+        <v>2987.64073723132</v>
       </c>
       <c r="E18">
-        <v>-4330.925823846602</v>
+        <v>-4270.60884975319</v>
       </c>
       <c r="F18">
-        <v>965.0715854945909</v>
+        <v>1025.388559588003</v>
       </c>
       <c r="G18">
         <v>2168.8</v>
@@ -2998,28 +2998,28 @@
         <v>476</v>
       </c>
       <c r="M18">
-        <v>51.63132982396061</v>
+        <v>54.85828793795815</v>
       </c>
       <c r="N18">
-        <v>424.3686701760394</v>
+        <v>421.1417120620418</v>
       </c>
       <c r="O18">
-        <v>112.4576975966504</v>
+        <v>111.6025536964411</v>
       </c>
       <c r="P18">
-        <v>311.910972579389</v>
+        <v>309.5391583656008</v>
       </c>
       <c r="Q18">
-        <v>676.910972579389</v>
+        <v>674.5391583656008</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1275257095361623</v>
+        <v>0.1282814693738725</v>
       </c>
       <c r="T18">
-        <v>1.887429781435619</v>
+        <v>1.904883819258026</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.219208601113777</v>
+        <v>8.676902212812967</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3044,22 +3044,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1131584445803142</v>
+        <v>0.1129036931502521</v>
       </c>
       <c r="C19">
-        <v>4131.052177643317</v>
+        <v>4082.077436958988</v>
       </c>
       <c r="D19">
-        <v>2987.64073723132</v>
+        <v>2998.982970640402</v>
       </c>
       <c r="E19">
-        <v>-4270.60884975319</v>
+        <v>-4210.291875659778</v>
       </c>
       <c r="F19">
-        <v>1025.388559588003</v>
+        <v>1085.705533681415</v>
       </c>
       <c r="G19">
         <v>2168.8</v>
@@ -3080,28 +3080,28 @@
         <v>476</v>
       </c>
       <c r="M19">
-        <v>54.85828793795815</v>
+        <v>58.08524605195569</v>
       </c>
       <c r="N19">
-        <v>421.1417120620418</v>
+        <v>417.9147539480443</v>
       </c>
       <c r="O19">
-        <v>111.6025536964411</v>
+        <v>110.7474097962318</v>
       </c>
       <c r="P19">
-        <v>309.5391583656008</v>
+        <v>307.1673441518126</v>
       </c>
       <c r="Q19">
-        <v>674.5391583656008</v>
+        <v>672.1673441518126</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1282814693738725</v>
+        <v>0.1290556623783562</v>
       </c>
       <c r="T19">
-        <v>1.904883819258026</v>
+        <v>1.922763565320004</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.676902212812967</v>
+        <v>8.194852089878914</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3126,22 +3126,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1129036931502521</v>
+        <v>0.1126489417201899</v>
       </c>
       <c r="C20">
-        <v>4082.077436958986</v>
+        <v>4033.189143422712</v>
       </c>
       <c r="D20">
-        <v>2998.982970640401</v>
+        <v>3010.411651197538</v>
       </c>
       <c r="E20">
-        <v>-4210.291875659778</v>
+        <v>-4149.974901566366</v>
       </c>
       <c r="F20">
-        <v>1085.705533681415</v>
+        <v>1146.022507774827</v>
       </c>
       <c r="G20">
         <v>2168.8</v>
@@ -3162,28 +3162,28 @@
         <v>476</v>
       </c>
       <c r="M20">
-        <v>58.08524605195568</v>
+        <v>61.31220416595323</v>
       </c>
       <c r="N20">
-        <v>417.9147539480443</v>
+        <v>414.6877958340468</v>
       </c>
       <c r="O20">
-        <v>110.7474097962318</v>
+        <v>109.8922658960224</v>
       </c>
       <c r="P20">
-        <v>307.1673441518126</v>
+        <v>304.7955299380244</v>
       </c>
       <c r="Q20">
-        <v>672.1673441518126</v>
+        <v>669.7955299380244</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1290556623783562</v>
+        <v>0.1298489712594937</v>
       </c>
       <c r="T20">
-        <v>1.922763565320004</v>
+        <v>1.941084786593389</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.194852089878914</v>
+        <v>7.763544085148444</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3208,22 +3208,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1126489417201899</v>
+        <v>0.1125117902901278</v>
       </c>
       <c r="C21">
-        <v>4033.189143422712</v>
+        <v>3979.06121419291</v>
       </c>
       <c r="D21">
-        <v>3010.411651197538</v>
+        <v>3016.600696061148</v>
       </c>
       <c r="E21">
-        <v>-4149.974901566366</v>
+        <v>-4089.657927472954</v>
       </c>
       <c r="F21">
-        <v>1146.022507774827</v>
+        <v>1206.339481868239</v>
       </c>
       <c r="G21">
         <v>2168.8</v>
@@ -3244,45 +3244,45 @@
         <v>476</v>
       </c>
       <c r="M21">
-        <v>61.31220416595323</v>
+        <v>65.50423386544536</v>
       </c>
       <c r="N21">
-        <v>414.6877958340468</v>
+        <v>410.4957661345546</v>
       </c>
       <c r="O21">
-        <v>109.8922658960224</v>
+        <v>108.781378025657</v>
       </c>
       <c r="P21">
-        <v>304.7955299380244</v>
+        <v>301.7143881088977</v>
       </c>
       <c r="Q21">
-        <v>669.7955299380244</v>
+        <v>666.7143881088977</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1298489712594937</v>
+        <v>0.1306621128626597</v>
       </c>
       <c r="T21">
-        <v>1.941084786593389</v>
+        <v>1.959864038398609</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.265</v>
       </c>
       <c r="W21">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.763544085148444</v>
+        <v>7.266705858704782</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3290,22 +3290,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1125117902901278</v>
+        <v>0.1122629188600657</v>
       </c>
       <c r="C22">
-        <v>3979.06121419291</v>
+        <v>3930.039948172986</v>
       </c>
       <c r="D22">
-        <v>3016.600696061148</v>
+        <v>3027.896404134636</v>
       </c>
       <c r="E22">
-        <v>-4089.657927472954</v>
+        <v>-4029.340953379542</v>
       </c>
       <c r="F22">
-        <v>1206.339481868239</v>
+        <v>1266.656455961651</v>
       </c>
       <c r="G22">
         <v>2168.8</v>
@@ -3326,28 +3326,28 @@
         <v>476</v>
       </c>
       <c r="M22">
-        <v>65.50423386544536</v>
+        <v>68.77944555871763</v>
       </c>
       <c r="N22">
-        <v>410.4957661345546</v>
+        <v>407.2205544412824</v>
       </c>
       <c r="O22">
-        <v>108.781378025657</v>
+        <v>107.9134469269398</v>
       </c>
       <c r="P22">
-        <v>301.7143881088977</v>
+        <v>299.3071075143425</v>
       </c>
       <c r="Q22">
-        <v>666.7143881088977</v>
+        <v>664.3071075143425</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1306621128626597</v>
+        <v>0.1314958403291971</v>
       </c>
       <c r="T22">
-        <v>1.959864038398609</v>
+        <v>1.979118714300163</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.266705858704782</v>
+        <v>6.920672246385507</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3372,22 +3372,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1122629188600657</v>
+        <v>0.1120140474300035</v>
       </c>
       <c r="C23">
-        <v>3930.039948172986</v>
+        <v>3881.103594014846</v>
       </c>
       <c r="D23">
-        <v>3027.896404134636</v>
+        <v>3039.277024069908</v>
       </c>
       <c r="E23">
-        <v>-4029.340953379542</v>
+        <v>-3969.02397928613</v>
       </c>
       <c r="F23">
-        <v>1266.65645596165</v>
+        <v>1326.973430055062</v>
       </c>
       <c r="G23">
         <v>2168.8</v>
@@ -3408,28 +3408,28 @@
         <v>476</v>
       </c>
       <c r="M23">
-        <v>68.77944555871761</v>
+        <v>72.05465725198989</v>
       </c>
       <c r="N23">
-        <v>407.2205544412824</v>
+        <v>403.9453427480101</v>
       </c>
       <c r="O23">
-        <v>107.9134469269398</v>
+        <v>107.0455158282227</v>
       </c>
       <c r="P23">
-        <v>299.3071075143425</v>
+        <v>296.8998269197874</v>
       </c>
       <c r="Q23">
-        <v>664.3071075143425</v>
+        <v>661.8998269197874</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1314958403291971</v>
+        <v>0.1323509454230815</v>
       </c>
       <c r="T23">
-        <v>1.979118714300163</v>
+        <v>1.998867099840218</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.920672246385508</v>
+        <v>6.606096235186166</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3454,22 +3454,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1120140474300035</v>
+        <v>0.1117651759999414</v>
       </c>
       <c r="C24">
-        <v>3881.103594014846</v>
+        <v>3832.25311277724</v>
       </c>
       <c r="D24">
-        <v>3039.277024069908</v>
+        <v>3050.743516925714</v>
       </c>
       <c r="E24">
-        <v>-3969.02397928613</v>
+        <v>-3908.707005192718</v>
       </c>
       <c r="F24">
-        <v>1326.973430055062</v>
+        <v>1387.290404148474</v>
       </c>
       <c r="G24">
         <v>2168.8</v>
@@ -3490,28 +3490,28 @@
         <v>476</v>
       </c>
       <c r="M24">
-        <v>72.05465725198989</v>
+        <v>75.32986894526216</v>
       </c>
       <c r="N24">
-        <v>403.9453427480101</v>
+        <v>400.6701310547379</v>
       </c>
       <c r="O24">
-        <v>107.0455158282227</v>
+        <v>106.1775847295055</v>
       </c>
       <c r="P24">
-        <v>296.8998269197874</v>
+        <v>294.4925463252323</v>
       </c>
       <c r="Q24">
-        <v>661.8998269197874</v>
+        <v>659.4925463252323</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1323509454230815</v>
+        <v>0.1332282610388849</v>
       </c>
       <c r="T24">
-        <v>1.998867099840218</v>
+        <v>2.019128430459237</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.606096235186166</v>
+        <v>6.318874659743289</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3536,22 +3536,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1117651759999414</v>
+        <v>0.1116927045698793</v>
       </c>
       <c r="C25">
-        <v>3832.25311277724</v>
+        <v>3775.291468334774</v>
       </c>
       <c r="D25">
-        <v>3050.743516925714</v>
+        <v>3054.09884657666</v>
       </c>
       <c r="E25">
-        <v>-3908.707005192718</v>
+        <v>-3848.390031099307</v>
       </c>
       <c r="F25">
-        <v>1387.290404148474</v>
+        <v>1447.607378241886</v>
       </c>
       <c r="G25">
         <v>2168.8</v>
@@ -3572,45 +3572,45 @@
         <v>476</v>
       </c>
       <c r="M25">
-        <v>75.32986894526216</v>
+        <v>80.05268801677632</v>
       </c>
       <c r="N25">
-        <v>400.6701310547379</v>
+        <v>395.9473119832237</v>
       </c>
       <c r="O25">
-        <v>106.1775847295055</v>
+        <v>104.9260376755543</v>
       </c>
       <c r="P25">
-        <v>294.4925463252323</v>
+        <v>291.0212743076694</v>
       </c>
       <c r="Q25">
-        <v>659.4925463252323</v>
+        <v>656.0212743076694</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1332282610388849</v>
+        <v>0.1341286639077359</v>
       </c>
       <c r="T25">
-        <v>2.019128430459237</v>
+        <v>2.039922953989282</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.265</v>
       </c>
       <c r="W25">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.318874659743289</v>
+        <v>5.946083907891346</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3618,22 +3618,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1116927045698793</v>
+        <v>0.1114511831398172</v>
       </c>
       <c r="C26">
-        <v>3775.291468334774</v>
+        <v>3726.210092530663</v>
       </c>
       <c r="D26">
-        <v>3054.09884657666</v>
+        <v>3065.334444865961</v>
       </c>
       <c r="E26">
-        <v>-3848.390031099307</v>
+        <v>-3788.073057005895</v>
       </c>
       <c r="F26">
-        <v>1447.607378241886</v>
+        <v>1507.924352335298</v>
       </c>
       <c r="G26">
         <v>2168.8</v>
@@ -3654,28 +3654,28 @@
         <v>476</v>
       </c>
       <c r="M26">
-        <v>80.05268801677632</v>
+        <v>83.38821668414199</v>
       </c>
       <c r="N26">
-        <v>395.9473119832237</v>
+        <v>392.611783315858</v>
       </c>
       <c r="O26">
-        <v>104.9260376755543</v>
+        <v>104.0421225787024</v>
       </c>
       <c r="P26">
-        <v>291.0212743076694</v>
+        <v>288.5696607371556</v>
       </c>
       <c r="Q26">
-        <v>656.0212743076694</v>
+        <v>653.5696607371556</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1341286639077359</v>
+        <v>0.1350530775197562</v>
       </c>
       <c r="T26">
-        <v>2.039922953989282</v>
+        <v>2.061271998146795</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.946083907891346</v>
+        <v>5.708240551575692</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3700,22 +3700,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1114511831398172</v>
+        <v>0.111209661709755</v>
       </c>
       <c r="C27">
-        <v>3726.210092530663</v>
+        <v>3677.211690333064</v>
       </c>
       <c r="D27">
-        <v>3065.334444865961</v>
+        <v>3076.653016761774</v>
       </c>
       <c r="E27">
-        <v>-3788.073057005895</v>
+        <v>-3727.756082912483</v>
       </c>
       <c r="F27">
-        <v>1507.924352335298</v>
+        <v>1568.24132642871</v>
       </c>
       <c r="G27">
         <v>2168.8</v>
@@ -3736,28 +3736,28 @@
         <v>476</v>
       </c>
       <c r="M27">
-        <v>83.38821668414199</v>
+        <v>86.72374535150767</v>
       </c>
       <c r="N27">
-        <v>392.611783315858</v>
+        <v>389.2762546484923</v>
       </c>
       <c r="O27">
-        <v>104.0421225787024</v>
+        <v>103.1582074818505</v>
       </c>
       <c r="P27">
-        <v>288.5696607371556</v>
+        <v>286.1180471666419</v>
       </c>
       <c r="Q27">
-        <v>653.5696607371556</v>
+        <v>651.1180471666419</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1350530775197562</v>
+        <v>0.1360024752834527</v>
       </c>
       <c r="T27">
-        <v>2.061271998146795</v>
+        <v>2.083198043497754</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.708240551575692</v>
+        <v>5.48869283805355</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3782,22 +3782,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.111209661709755</v>
+        <v>0.1109681402796929</v>
       </c>
       <c r="C28">
-        <v>3677.211690333064</v>
+        <v>3628.297184274249</v>
       </c>
       <c r="D28">
-        <v>3076.653016761774</v>
+        <v>3088.055484796371</v>
       </c>
       <c r="E28">
-        <v>-3727.756082912483</v>
+        <v>-3667.43910881907</v>
       </c>
       <c r="F28">
-        <v>1568.24132642871</v>
+        <v>1628.558300522122</v>
       </c>
       <c r="G28">
         <v>2168.8</v>
@@ -3818,28 +3818,28 @@
         <v>476</v>
       </c>
       <c r="M28">
-        <v>86.72374535150767</v>
+        <v>90.05927401887335</v>
       </c>
       <c r="N28">
-        <v>389.2762546484923</v>
+        <v>385.9407259811267</v>
       </c>
       <c r="O28">
-        <v>103.1582074818505</v>
+        <v>102.2742923849986</v>
       </c>
       <c r="P28">
-        <v>286.1180471666419</v>
+        <v>283.6664335961281</v>
       </c>
       <c r="Q28">
-        <v>651.1180471666419</v>
+        <v>648.6664335961281</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1360024752834527</v>
+        <v>0.1369778839447848</v>
       </c>
       <c r="T28">
-        <v>2.083198043497754</v>
+        <v>2.105724802419972</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.48869283805355</v>
+        <v>5.285407918125641</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3864,22 +3864,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1109681402796929</v>
+        <v>0.1107266188496308</v>
       </c>
       <c r="C29">
-        <v>3628.297184274249</v>
+        <v>3579.467510613446</v>
       </c>
       <c r="D29">
-        <v>3088.055484796371</v>
+        <v>3099.54278522898</v>
       </c>
       <c r="E29">
-        <v>-3667.43910881907</v>
+        <v>-3607.122134725659</v>
       </c>
       <c r="F29">
-        <v>1628.558300522122</v>
+        <v>1688.875274615534</v>
       </c>
       <c r="G29">
         <v>2168.8</v>
@@ -3900,28 +3900,28 @@
         <v>476</v>
       </c>
       <c r="M29">
-        <v>90.05927401887335</v>
+        <v>93.39480268623905</v>
       </c>
       <c r="N29">
-        <v>385.9407259811267</v>
+        <v>382.605197313761</v>
       </c>
       <c r="O29">
-        <v>102.2742923849986</v>
+        <v>101.3903772881467</v>
       </c>
       <c r="P29">
-        <v>283.6664335961281</v>
+        <v>281.2148200256143</v>
       </c>
       <c r="Q29">
-        <v>648.6664335961281</v>
+        <v>646.2148200256142</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1369778839447848</v>
+        <v>0.1379803872911538</v>
       </c>
       <c r="T29">
-        <v>2.105724802419972</v>
+        <v>2.128877304645585</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.285407918125641</v>
+        <v>5.096643349621153</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3946,22 +3946,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1107266188496308</v>
+        <v>0.1104850974195686</v>
       </c>
       <c r="C30">
-        <v>3579.467510613446</v>
+        <v>3530.723619593121</v>
       </c>
       <c r="D30">
-        <v>3099.54278522898</v>
+        <v>3111.115868302066</v>
       </c>
       <c r="E30">
-        <v>-3607.122134725659</v>
+        <v>-3546.805160632247</v>
       </c>
       <c r="F30">
-        <v>1688.875274615534</v>
+        <v>1749.192248708946</v>
       </c>
       <c r="G30">
         <v>2168.8</v>
@@ -3982,28 +3982,28 @@
         <v>476</v>
       </c>
       <c r="M30">
-        <v>93.39480268623905</v>
+        <v>96.73033135360473</v>
       </c>
       <c r="N30">
-        <v>382.605197313761</v>
+        <v>379.2696686463953</v>
       </c>
       <c r="O30">
-        <v>101.3903772881467</v>
+        <v>100.5064621912948</v>
       </c>
       <c r="P30">
-        <v>281.2148200256143</v>
+        <v>278.7632064551005</v>
       </c>
       <c r="Q30">
-        <v>646.2148200256142</v>
+        <v>643.7632064551005</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1379803872911538</v>
+        <v>0.1390111301684065</v>
       </c>
       <c r="T30">
-        <v>2.128877304645585</v>
+        <v>2.152681990032483</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.096643349621153</v>
+        <v>4.920897027220423</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4028,22 +4028,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1104850974195686</v>
+        <v>0.1102435759895065</v>
       </c>
       <c r="C31">
-        <v>3530.723619593121</v>
+        <v>3482.066475700994</v>
       </c>
       <c r="D31">
-        <v>3111.115868302066</v>
+        <v>3122.775698503352</v>
       </c>
       <c r="E31">
-        <v>-3546.805160632247</v>
+        <v>-3486.488186538835</v>
       </c>
       <c r="F31">
-        <v>1749.192248708946</v>
+        <v>1809.509222802358</v>
       </c>
       <c r="G31">
         <v>2168.8</v>
@@ -4064,28 +4064,28 @@
         <v>476</v>
       </c>
       <c r="M31">
-        <v>96.7303313536047</v>
+        <v>100.0658600209704</v>
       </c>
       <c r="N31">
-        <v>379.2696686463953</v>
+        <v>375.9341399790296</v>
       </c>
       <c r="O31">
-        <v>100.5064621912948</v>
+        <v>99.62254709444285</v>
       </c>
       <c r="P31">
-        <v>278.7632064551005</v>
+        <v>276.3115928845868</v>
       </c>
       <c r="Q31">
-        <v>643.7632064551005</v>
+        <v>641.3115928845868</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1390111301684065</v>
+        <v>0.1400713228421521</v>
       </c>
       <c r="T31">
-        <v>2.152681990032483</v>
+        <v>2.177166809287578</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.920897027220425</v>
+        <v>4.756867126313077</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4110,22 +4110,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1102435759895065</v>
+        <v>0.1100020545594443</v>
       </c>
       <c r="C32">
-        <v>3482.066475700994</v>
+        <v>3433.497057938003</v>
       </c>
       <c r="D32">
-        <v>3122.775698503352</v>
+        <v>3134.523254833773</v>
       </c>
       <c r="E32">
-        <v>-3486.488186538835</v>
+        <v>-3426.171212445423</v>
       </c>
       <c r="F32">
-        <v>1809.509222802358</v>
+        <v>1869.82619689577</v>
       </c>
       <c r="G32">
         <v>2168.8</v>
@@ -4146,28 +4146,28 @@
         <v>476</v>
       </c>
       <c r="M32">
-        <v>100.0658600209704</v>
+        <v>103.4013886883361</v>
       </c>
       <c r="N32">
-        <v>375.9341399790296</v>
+        <v>372.5986113116639</v>
       </c>
       <c r="O32">
-        <v>99.62254709444285</v>
+        <v>98.73863199759096</v>
       </c>
       <c r="P32">
-        <v>276.3115928845868</v>
+        <v>273.859979314073</v>
       </c>
       <c r="Q32">
-        <v>641.3115928845868</v>
+        <v>638.8599793140729</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1400713228421521</v>
+        <v>0.1411622457383251</v>
       </c>
       <c r="T32">
-        <v>2.177166809287578</v>
+        <v>2.202361333448618</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.756867126313077</v>
+        <v>4.603419799657816</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4192,22 +4192,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1100020545594443</v>
+        <v>0.1103485331293822</v>
       </c>
       <c r="C33">
-        <v>3433.497057938003</v>
+        <v>3356.354834964109</v>
       </c>
       <c r="D33">
-        <v>3134.523254833773</v>
+        <v>3117.698005953291</v>
       </c>
       <c r="E33">
-        <v>-3426.171212445423</v>
+        <v>-3365.854238352011</v>
       </c>
       <c r="F33">
-        <v>1869.82619689577</v>
+        <v>1930.143170989182</v>
       </c>
       <c r="G33">
         <v>2168.8</v>
@@ -4228,45 +4228,45 @@
         <v>476</v>
       </c>
       <c r="M33">
-        <v>103.4013886883361</v>
+        <v>111.5622752831747</v>
       </c>
       <c r="N33">
-        <v>372.5986113116639</v>
+        <v>364.4377247168253</v>
       </c>
       <c r="O33">
-        <v>98.73863199759096</v>
+        <v>96.57599704995872</v>
       </c>
       <c r="P33">
-        <v>273.859979314073</v>
+        <v>267.8617276668666</v>
       </c>
       <c r="Q33">
-        <v>638.8599793140729</v>
+        <v>632.8617276668666</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1411622457383251</v>
+        <v>0.1422852546020327</v>
       </c>
       <c r="T33">
-        <v>2.202361333448618</v>
+        <v>2.228296873026159</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.265</v>
       </c>
       <c r="W33">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.603419799657816</v>
+        <v>4.266675260896083</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4274,22 +4274,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1103485331293822</v>
+        <v>0.1101253866993201</v>
       </c>
       <c r="C34">
-        <v>3356.354834964109</v>
+        <v>3306.853235884179</v>
       </c>
       <c r="D34">
-        <v>3117.698005953291</v>
+        <v>3128.513380966772</v>
       </c>
       <c r="E34">
-        <v>-3365.854238352011</v>
+        <v>-3305.537264258599</v>
       </c>
       <c r="F34">
-        <v>1930.143170989182</v>
+        <v>1990.460145082594</v>
       </c>
       <c r="G34">
         <v>2168.8</v>
@@ -4310,28 +4310,28 @@
         <v>476</v>
       </c>
       <c r="M34">
-        <v>111.5622752831747</v>
+        <v>115.0485963857739</v>
       </c>
       <c r="N34">
-        <v>364.4377247168253</v>
+        <v>360.9514036142261</v>
       </c>
       <c r="O34">
-        <v>96.57599704995872</v>
+        <v>95.65212195776992</v>
       </c>
       <c r="P34">
-        <v>267.8617276668666</v>
+        <v>265.2992816564562</v>
       </c>
       <c r="Q34">
-        <v>632.8617276668666</v>
+        <v>630.2992816564562</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1422852546020327</v>
+        <v>0.1434417861183882</v>
       </c>
       <c r="T34">
-        <v>2.228296873026159</v>
+        <v>2.25500660781497</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.266675260896083</v>
+        <v>4.137382071171959</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4356,22 +4356,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1101253866993201</v>
+        <v>0.109902240269258</v>
       </c>
       <c r="C35">
-        <v>3306.853235884179</v>
+        <v>3257.426935649152</v>
       </c>
       <c r="D35">
-        <v>3128.513380966772</v>
+        <v>3139.404054825158</v>
       </c>
       <c r="E35">
-        <v>-3305.537264258599</v>
+        <v>-3245.220290165187</v>
       </c>
       <c r="F35">
-        <v>1990.460145082594</v>
+        <v>2050.777119176006</v>
       </c>
       <c r="G35">
         <v>2168.8</v>
@@ -4392,28 +4392,28 @@
         <v>476</v>
       </c>
       <c r="M35">
-        <v>115.0485963857739</v>
+        <v>118.5349174883731</v>
       </c>
       <c r="N35">
-        <v>360.9514036142261</v>
+        <v>357.4650825116269</v>
       </c>
       <c r="O35">
-        <v>95.65212195776992</v>
+        <v>94.72824686558113</v>
       </c>
       <c r="P35">
-        <v>265.2992816564562</v>
+        <v>262.7368356460457</v>
       </c>
       <c r="Q35">
-        <v>630.2992816564562</v>
+        <v>627.7368356460457</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1434417861183882</v>
+        <v>0.1446333640443302</v>
       </c>
       <c r="T35">
-        <v>2.25500660781497</v>
+        <v>2.282525728506472</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.137382071171959</v>
+        <v>4.015694363196312</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4438,22 +4438,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.109902240269258</v>
+        <v>0.1105794688391958</v>
       </c>
       <c r="C36">
-        <v>3257.426935649152</v>
+        <v>3164.289468325331</v>
       </c>
       <c r="D36">
-        <v>3139.404054825158</v>
+        <v>3106.583561594748</v>
       </c>
       <c r="E36">
-        <v>-3245.220290165187</v>
+        <v>-3184.903316071775</v>
       </c>
       <c r="F36">
-        <v>2050.777119176006</v>
+        <v>2111.094093269417</v>
       </c>
       <c r="G36">
         <v>2168.8</v>
@@ -4474,45 +4474,45 @@
         <v>476</v>
       </c>
       <c r="M36">
-        <v>118.5349174883731</v>
+        <v>129.4100679174153</v>
       </c>
       <c r="N36">
-        <v>357.4650825116269</v>
+        <v>346.5899320825847</v>
       </c>
       <c r="O36">
-        <v>94.72824686558113</v>
+        <v>91.84633200188495</v>
       </c>
       <c r="P36">
-        <v>262.7368356460457</v>
+        <v>254.7436000806998</v>
       </c>
       <c r="Q36">
-        <v>627.7368356460457</v>
+        <v>619.7436000806997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1446333640443302</v>
+        <v>0.1458616059064551</v>
       </c>
       <c r="T36">
-        <v>2.282525728506472</v>
+        <v>2.310891591373098</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.265</v>
       </c>
       <c r="W36">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.015694363196312</v>
+        <v>3.678230045468839</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4520,22 +4520,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1105794688391958</v>
+        <v>0.1103820474091337</v>
       </c>
       <c r="C37">
-        <v>3164.289468325331</v>
+        <v>3113.469036908124</v>
       </c>
       <c r="D37">
-        <v>3106.583561594748</v>
+        <v>3116.080104270954</v>
       </c>
       <c r="E37">
-        <v>-3184.903316071775</v>
+        <v>-3124.586341978363</v>
       </c>
       <c r="F37">
-        <v>2111.094093269417</v>
+        <v>2171.41106736283</v>
       </c>
       <c r="G37">
         <v>2168.8</v>
@@ -4556,28 +4556,28 @@
         <v>476</v>
       </c>
       <c r="M37">
-        <v>129.4100679174153</v>
+        <v>133.1074984293415</v>
       </c>
       <c r="N37">
-        <v>346.5899320825847</v>
+        <v>342.8925015706585</v>
       </c>
       <c r="O37">
-        <v>91.84633200188495</v>
+        <v>90.86651291622451</v>
       </c>
       <c r="P37">
-        <v>254.7436000806998</v>
+        <v>252.025988654434</v>
       </c>
       <c r="Q37">
-        <v>619.7436000806997</v>
+        <v>617.0259886544341</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1458616059064551</v>
+        <v>0.1471282303267714</v>
       </c>
       <c r="T37">
-        <v>2.310891591373098</v>
+        <v>2.340143887454305</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.678230045468839</v>
+        <v>3.576056988650259</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4602,22 +4602,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1103820474091337</v>
+        <v>0.1109460859790716</v>
       </c>
       <c r="C38">
-        <v>3113.469036908124</v>
+        <v>3026.172861540984</v>
       </c>
       <c r="D38">
-        <v>3116.080104270953</v>
+        <v>3089.100902997226</v>
       </c>
       <c r="E38">
-        <v>-3124.586341978364</v>
+        <v>-3064.269367884951</v>
       </c>
       <c r="F38">
-        <v>2171.411067362829</v>
+        <v>2231.728041456241</v>
       </c>
       <c r="G38">
         <v>2168.8</v>
@@ -4638,45 +4638,45 @@
         <v>476</v>
       </c>
       <c r="M38">
-        <v>133.1074984293414</v>
+        <v>143.0537674573451</v>
       </c>
       <c r="N38">
-        <v>342.8925015706586</v>
+        <v>332.9462325426549</v>
       </c>
       <c r="O38">
-        <v>90.86651291622452</v>
+        <v>88.23075162380356</v>
       </c>
       <c r="P38">
-        <v>252.0259886544341</v>
+        <v>244.7154809188514</v>
       </c>
       <c r="Q38">
-        <v>617.0259886544341</v>
+        <v>609.7154809188514</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1471282303267714</v>
+        <v>0.1484350650461453</v>
       </c>
       <c r="T38">
-        <v>2.340143887454305</v>
+        <v>2.370324827855551</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.265</v>
       </c>
       <c r="W38">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.576056988650261</v>
+        <v>3.327420231291223</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4684,22 +4684,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1109460859790716</v>
+        <v>0.1107692445490094</v>
       </c>
       <c r="C39">
-        <v>3026.172861540984</v>
+        <v>2974.264189330784</v>
       </c>
       <c r="D39">
-        <v>3089.100902997226</v>
+        <v>3097.509204880438</v>
       </c>
       <c r="E39">
-        <v>-3064.269367884951</v>
+        <v>-3003.95239379154</v>
       </c>
       <c r="F39">
-        <v>2231.728041456241</v>
+        <v>2292.045015549653</v>
       </c>
       <c r="G39">
         <v>2168.8</v>
@@ -4720,28 +4720,28 @@
         <v>476</v>
       </c>
       <c r="M39">
-        <v>143.0537674573451</v>
+        <v>146.9200854967328</v>
       </c>
       <c r="N39">
-        <v>332.9462325426549</v>
+        <v>329.0799145032672</v>
       </c>
       <c r="O39">
-        <v>88.23075162380356</v>
+        <v>87.20617734336582</v>
       </c>
       <c r="P39">
-        <v>244.7154809188514</v>
+        <v>241.8737371599014</v>
       </c>
       <c r="Q39">
-        <v>609.7154809188514</v>
+        <v>606.8737371599013</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1484350650461453</v>
+        <v>0.1497840557242088</v>
       </c>
       <c r="T39">
-        <v>2.370324827855551</v>
+        <v>2.401479346979417</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.327420231291223</v>
+        <v>3.239856540994086</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4766,22 +4766,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1107692445490094</v>
+        <v>0.1105924031189473</v>
       </c>
       <c r="C40">
-        <v>2974.264189330784</v>
+        <v>2922.401415591943</v>
       </c>
       <c r="D40">
-        <v>3097.509204880438</v>
+        <v>3105.963405235007</v>
       </c>
       <c r="E40">
-        <v>-3003.95239379154</v>
+        <v>-2943.635419698128</v>
       </c>
       <c r="F40">
-        <v>2292.045015549653</v>
+        <v>2352.361989643065</v>
       </c>
       <c r="G40">
         <v>2168.8</v>
@@ -4802,28 +4802,28 @@
         <v>476</v>
       </c>
       <c r="M40">
-        <v>146.9200854967328</v>
+        <v>150.7864035361205</v>
       </c>
       <c r="N40">
-        <v>329.0799145032672</v>
+        <v>325.2135964638795</v>
       </c>
       <c r="O40">
-        <v>87.20617734336582</v>
+        <v>86.18160306292808</v>
       </c>
       <c r="P40">
-        <v>241.8737371599014</v>
+        <v>239.0319934009514</v>
       </c>
       <c r="Q40">
-        <v>606.8737371599013</v>
+        <v>604.0319934009515</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1497840557242088</v>
+        <v>0.1511772756048317</v>
       </c>
       <c r="T40">
-        <v>2.401479346979417</v>
+        <v>2.43365532574669</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.239856540994086</v>
+        <v>3.156783296353212</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4848,22 +4848,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1105924031189473</v>
+        <v>0.1104155616888852</v>
       </c>
       <c r="C41">
-        <v>2922.401415591943</v>
+        <v>2870.584917172596</v>
       </c>
       <c r="D41">
-        <v>3105.963405235007</v>
+        <v>3114.463880909073</v>
       </c>
       <c r="E41">
-        <v>-2943.635419698128</v>
+        <v>-2883.318445604716</v>
       </c>
       <c r="F41">
-        <v>2352.361989643065</v>
+        <v>2412.678963736477</v>
       </c>
       <c r="G41">
         <v>2168.8</v>
@@ -4884,28 +4884,28 @@
         <v>476</v>
       </c>
       <c r="M41">
-        <v>150.7864035361205</v>
+        <v>154.6527215755082</v>
       </c>
       <c r="N41">
-        <v>325.2135964638795</v>
+        <v>321.3472784244918</v>
       </c>
       <c r="O41">
-        <v>86.18160306292808</v>
+        <v>85.15702878249034</v>
       </c>
       <c r="P41">
-        <v>239.0319934009514</v>
+        <v>236.1902496420015</v>
       </c>
       <c r="Q41">
-        <v>604.0319934009515</v>
+        <v>601.1902496420015</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1511772756048317</v>
+        <v>0.152616936148142</v>
       </c>
       <c r="T41">
-        <v>2.43365532574669</v>
+        <v>2.466903837139537</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.156783296353212</v>
+        <v>3.077863713944382</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4930,22 +4930,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1104155616888852</v>
+        <v>0.110238720258823</v>
       </c>
       <c r="C42">
-        <v>2870.584917172596</v>
+        <v>2818.81507505767</v>
       </c>
       <c r="D42">
-        <v>3114.463880909073</v>
+        <v>3123.011012887559</v>
       </c>
       <c r="E42">
-        <v>-2883.318445604716</v>
+        <v>-2823.001471511304</v>
       </c>
       <c r="F42">
-        <v>2412.678963736477</v>
+        <v>2472.995937829889</v>
       </c>
       <c r="G42">
         <v>2168.8</v>
@@ -4966,28 +4966,28 @@
         <v>476</v>
       </c>
       <c r="M42">
-        <v>154.6527215755082</v>
+        <v>158.5190396148959</v>
       </c>
       <c r="N42">
-        <v>321.3472784244918</v>
+        <v>317.4809603851041</v>
       </c>
       <c r="O42">
-        <v>85.15702878249034</v>
+        <v>84.1324545020526</v>
       </c>
       <c r="P42">
-        <v>236.1902496420015</v>
+        <v>233.3485058830515</v>
       </c>
       <c r="Q42">
-        <v>601.1902496420015</v>
+        <v>598.3485058830515</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.152616936148142</v>
+        <v>0.1541053987437679</v>
       </c>
       <c r="T42">
-        <v>2.466903837139537</v>
+        <v>2.501279416715193</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.077863713944382</v>
+        <v>3.002793867262811</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5012,22 +5012,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.110238720258823</v>
+        <v>0.1124697388287609</v>
       </c>
       <c r="C43">
-        <v>2818.81507505767</v>
+        <v>2653.990483471283</v>
       </c>
       <c r="D43">
-        <v>3123.011012887559</v>
+        <v>3018.503395394584</v>
       </c>
       <c r="E43">
-        <v>-2823.001471511304</v>
+        <v>-2762.684497417892</v>
       </c>
       <c r="F43">
-        <v>2472.995937829889</v>
+        <v>2533.312911923301</v>
       </c>
       <c r="G43">
         <v>2168.8</v>
@@ -5048,45 +5048,45 @@
         <v>476</v>
       </c>
       <c r="M43">
-        <v>158.5190396148959</v>
+        <v>182.1451983672854</v>
       </c>
       <c r="N43">
-        <v>317.4809603851041</v>
+        <v>293.8548016327146</v>
       </c>
       <c r="O43">
-        <v>84.1324545020526</v>
+        <v>77.87152243266938</v>
       </c>
       <c r="P43">
-        <v>233.3485058830515</v>
+        <v>215.9832792000452</v>
       </c>
       <c r="Q43">
-        <v>598.3485058830515</v>
+        <v>580.9832792000452</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1541053987437679</v>
+        <v>0.1556451876357947</v>
       </c>
       <c r="T43">
-        <v>2.501279416715193</v>
+        <v>2.536840361103803</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.265</v>
       </c>
       <c r="W43">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.002793867262811</v>
+        <v>2.613299742550299</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5094,22 +5094,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1124697388287609</v>
+        <v>0.1123502273986988</v>
       </c>
       <c r="C44">
-        <v>2653.990483471282</v>
+        <v>2599.094161891495</v>
       </c>
       <c r="D44">
-        <v>3018.503395394584</v>
+        <v>3023.924047908208</v>
       </c>
       <c r="E44">
-        <v>-2762.684497417892</v>
+        <v>-2702.36752332448</v>
       </c>
       <c r="F44">
-        <v>2533.312911923301</v>
+        <v>2593.629886016713</v>
       </c>
       <c r="G44">
         <v>2168.8</v>
@@ -5130,28 +5130,28 @@
         <v>476</v>
       </c>
       <c r="M44">
-        <v>182.1451983672853</v>
+        <v>186.4819888046017</v>
       </c>
       <c r="N44">
-        <v>293.8548016327147</v>
+        <v>289.5180111953983</v>
       </c>
       <c r="O44">
-        <v>77.87152243266939</v>
+        <v>76.72227296678057</v>
       </c>
       <c r="P44">
-        <v>215.9832792000453</v>
+        <v>212.7957382286178</v>
       </c>
       <c r="Q44">
-        <v>580.9832792000452</v>
+        <v>577.7957382286178</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1556451876357947</v>
+        <v>0.1572390042082435</v>
       </c>
       <c r="T44">
-        <v>2.536840361103803</v>
+        <v>2.573649057927101</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.6132997425503</v>
+        <v>2.55252532993285</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5176,22 +5176,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1123502273986988</v>
+        <v>0.1134919759686367</v>
       </c>
       <c r="C45">
-        <v>2599.094161891495</v>
+        <v>2487.773196440236</v>
       </c>
       <c r="D45">
-        <v>3023.924047908208</v>
+        <v>2972.92005655036</v>
       </c>
       <c r="E45">
-        <v>-2702.36752332448</v>
+        <v>-2642.050549231068</v>
       </c>
       <c r="F45">
-        <v>2593.629886016713</v>
+        <v>2653.946860110125</v>
       </c>
       <c r="G45">
         <v>2168.8</v>
@@ -5212,45 +5212,45 @@
         <v>476</v>
       </c>
       <c r="M45">
-        <v>186.4819888046017</v>
+        <v>201.1691719963475</v>
       </c>
       <c r="N45">
-        <v>289.5180111953983</v>
+        <v>274.8308280036525</v>
       </c>
       <c r="O45">
-        <v>76.72227296678057</v>
+        <v>72.83016942096792</v>
       </c>
       <c r="P45">
-        <v>212.7957382286178</v>
+        <v>202.0006585826846</v>
       </c>
       <c r="Q45">
-        <v>577.7957382286178</v>
+        <v>567.0006585826845</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1572390042082435</v>
+        <v>0.1588897428011369</v>
       </c>
       <c r="T45">
-        <v>2.573649057927101</v>
+        <v>2.611772351065517</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.265</v>
       </c>
       <c r="W45">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.55252532993285</v>
+        <v>2.366167714845704</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5258,22 +5258,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1134919759686367</v>
+        <v>0.1134011295385745</v>
       </c>
       <c r="C46">
-        <v>2487.773196440236</v>
+        <v>2431.451409643859</v>
       </c>
       <c r="D46">
-        <v>2972.92005655036</v>
+        <v>2976.915243847396</v>
       </c>
       <c r="E46">
-        <v>-2642.050549231068</v>
+        <v>-2581.733575137656</v>
       </c>
       <c r="F46">
-        <v>2653.946860110125</v>
+        <v>2714.263834203537</v>
       </c>
       <c r="G46">
         <v>2168.8</v>
@@ -5294,28 +5294,28 @@
         <v>476</v>
       </c>
       <c r="M46">
-        <v>201.1691719963475</v>
+        <v>205.7411986326281</v>
       </c>
       <c r="N46">
-        <v>274.8308280036525</v>
+        <v>270.2588013673719</v>
       </c>
       <c r="O46">
-        <v>72.83016942096792</v>
+        <v>71.61858236235356</v>
       </c>
       <c r="P46">
-        <v>202.0006585826846</v>
+        <v>198.6402190050184</v>
       </c>
       <c r="Q46">
-        <v>567.0006585826845</v>
+        <v>563.6402190050184</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1588897428011369</v>
+        <v>0.1606005082519537</v>
       </c>
       <c r="T46">
-        <v>2.611772351065517</v>
+        <v>2.651281945772602</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.366167714845704</v>
+        <v>2.313586210071356</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5340,22 +5340,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1134011295385745</v>
+        <v>0.1133102831085124</v>
       </c>
       <c r="C47">
-        <v>2431.451409643859</v>
+        <v>2375.140375239167</v>
       </c>
       <c r="D47">
-        <v>2976.915243847396</v>
+        <v>2980.921183536115</v>
       </c>
       <c r="E47">
-        <v>-2581.733575137656</v>
+        <v>-2521.416601044244</v>
       </c>
       <c r="F47">
-        <v>2714.263834203537</v>
+        <v>2774.580808296949</v>
       </c>
       <c r="G47">
         <v>2168.8</v>
@@ -5376,28 +5376,28 @@
         <v>476</v>
       </c>
       <c r="M47">
-        <v>205.7411986326281</v>
+        <v>210.3132252689087</v>
       </c>
       <c r="N47">
-        <v>270.2588013673719</v>
+        <v>265.6867747310913</v>
       </c>
       <c r="O47">
-        <v>71.61858236235356</v>
+        <v>70.40699530373919</v>
       </c>
       <c r="P47">
-        <v>198.6402190050184</v>
+        <v>195.2797794273521</v>
       </c>
       <c r="Q47">
-        <v>563.6402190050184</v>
+        <v>560.2797794273521</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1606005082519537</v>
+        <v>0.162374635386134</v>
       </c>
       <c r="T47">
-        <v>2.651281945772602</v>
+        <v>2.692254858802172</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.313586210071356</v>
+        <v>2.2632908576785</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5422,22 +5422,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1133102831085124</v>
+        <v>0.1132194366784502</v>
       </c>
       <c r="C48">
-        <v>2375.140375239167</v>
+        <v>2318.840136692099</v>
       </c>
       <c r="D48">
-        <v>2980.921183536115</v>
+        <v>2984.93791908246</v>
       </c>
       <c r="E48">
-        <v>-2521.416601044244</v>
+        <v>-2461.099626950832</v>
       </c>
       <c r="F48">
-        <v>2774.580808296949</v>
+        <v>2834.897782390361</v>
       </c>
       <c r="G48">
         <v>2168.8</v>
@@ -5458,28 +5458,28 @@
         <v>476</v>
       </c>
       <c r="M48">
-        <v>210.3132252689087</v>
+        <v>214.8852519051894</v>
       </c>
       <c r="N48">
-        <v>265.6867747310913</v>
+        <v>261.1147480948106</v>
       </c>
       <c r="O48">
-        <v>70.40699530373919</v>
+        <v>69.19540824512482</v>
       </c>
       <c r="P48">
-        <v>195.2797794273521</v>
+        <v>191.9193398496858</v>
       </c>
       <c r="Q48">
-        <v>560.2797794273521</v>
+        <v>556.9193398496858</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.162374635386134</v>
+        <v>0.1642157107140571</v>
       </c>
       <c r="T48">
-        <v>2.692254858802172</v>
+        <v>2.734773919493235</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.2632908576785</v>
+        <v>2.215135733047043</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5504,22 +5504,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1132194366784502</v>
+        <v>0.1131285902483881</v>
       </c>
       <c r="C49">
-        <v>2318.840136692099</v>
+        <v>2262.55073770319</v>
       </c>
       <c r="D49">
-        <v>2984.93791908246</v>
+        <v>2988.965494186963</v>
       </c>
       <c r="E49">
-        <v>-2461.099626950832</v>
+        <v>-2400.78265285742</v>
       </c>
       <c r="F49">
-        <v>2834.897782390361</v>
+        <v>2895.214756483773</v>
       </c>
       <c r="G49">
         <v>2168.8</v>
@@ -5540,28 +5540,28 @@
         <v>476</v>
       </c>
       <c r="M49">
-        <v>214.8852519051894</v>
+        <v>219.45727854147</v>
       </c>
       <c r="N49">
-        <v>261.1147480948106</v>
+        <v>256.54272145853</v>
       </c>
       <c r="O49">
-        <v>69.19540824512482</v>
+        <v>67.98382118651044</v>
       </c>
       <c r="P49">
-        <v>191.9193398496858</v>
+        <v>188.5589002720195</v>
       </c>
       <c r="Q49">
-        <v>556.9193398496858</v>
+        <v>553.5589002720195</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1642157107140571</v>
+        <v>0.1661275966315156</v>
       </c>
       <c r="T49">
-        <v>2.734773919493235</v>
+        <v>2.778928328672416</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.215135733047043</v>
+        <v>2.168987071941896</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5586,22 +5586,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1131285902483881</v>
+        <v>0.113037743818326</v>
       </c>
       <c r="C50">
-        <v>2262.550737703191</v>
+        <v>2206.272222209155</v>
       </c>
       <c r="D50">
-        <v>2988.965494186963</v>
+        <v>2993.003952786339</v>
       </c>
       <c r="E50">
-        <v>-2400.782652857421</v>
+        <v>-2340.465678764008</v>
       </c>
       <c r="F50">
-        <v>2895.214756483772</v>
+        <v>2955.531730577185</v>
       </c>
       <c r="G50">
         <v>2168.8</v>
@@ -5622,28 +5622,28 @@
         <v>476</v>
       </c>
       <c r="M50">
-        <v>219.45727854147</v>
+        <v>224.0293051777506</v>
       </c>
       <c r="N50">
-        <v>256.54272145853</v>
+        <v>251.9706948222494</v>
       </c>
       <c r="O50">
-        <v>67.98382118651045</v>
+        <v>66.77223412789608</v>
       </c>
       <c r="P50">
-        <v>188.5589002720196</v>
+        <v>185.1984606943533</v>
       </c>
       <c r="Q50">
-        <v>553.5589002720196</v>
+        <v>550.1984606943533</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1661275966315156</v>
+        <v>0.1681144584673059</v>
       </c>
       <c r="T50">
-        <v>2.778928328672416</v>
+        <v>2.824814283309604</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.168987071941896</v>
+        <v>2.124722029657367</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5668,22 +5668,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.113037743818326</v>
+        <v>0.1129468973882639</v>
       </c>
       <c r="C51">
-        <v>2206.272222209155</v>
+        <v>2150.004634384483</v>
       </c>
       <c r="D51">
-        <v>2993.003952786339</v>
+        <v>2997.053339055079</v>
       </c>
       <c r="E51">
-        <v>-2340.465678764008</v>
+        <v>-2280.148704670597</v>
       </c>
       <c r="F51">
-        <v>2955.531730577185</v>
+        <v>3015.848704670596</v>
       </c>
       <c r="G51">
         <v>2168.8</v>
@@ -5704,28 +5704,28 @@
         <v>476</v>
       </c>
       <c r="M51">
-        <v>224.0293051777506</v>
+        <v>228.6013318140312</v>
       </c>
       <c r="N51">
-        <v>251.9706948222494</v>
+        <v>247.3986681859688</v>
       </c>
       <c r="O51">
-        <v>66.77223412789608</v>
+        <v>65.56064706928173</v>
       </c>
       <c r="P51">
-        <v>185.1984606943533</v>
+        <v>181.8380211166871</v>
       </c>
       <c r="Q51">
-        <v>550.1984606943533</v>
+        <v>546.8380211166871</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1681144584673059</v>
+        <v>0.1701807947765277</v>
       </c>
       <c r="T51">
-        <v>2.824814283309604</v>
+        <v>2.87253567613228</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.124722029657367</v>
+        <v>2.08222758906422</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5750,22 +5750,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1129468973882639</v>
+        <v>0.1128560509582017</v>
       </c>
       <c r="C52">
-        <v>2150.004634384483</v>
+        <v>2093.748018643051</v>
       </c>
       <c r="D52">
-        <v>2997.053339055079</v>
+        <v>3001.113697407059</v>
       </c>
       <c r="E52">
-        <v>-2280.148704670597</v>
+        <v>-2219.831730577185</v>
       </c>
       <c r="F52">
-        <v>3015.848704670596</v>
+        <v>3076.165678764008</v>
       </c>
       <c r="G52">
         <v>2168.8</v>
@@ -5786,28 +5786,28 @@
         <v>476</v>
       </c>
       <c r="M52">
-        <v>228.6013318140312</v>
+        <v>233.1733584503118</v>
       </c>
       <c r="N52">
-        <v>247.3986681859688</v>
+        <v>242.8266415496882</v>
       </c>
       <c r="O52">
-        <v>65.56064706928173</v>
+        <v>64.34906001066737</v>
       </c>
       <c r="P52">
-        <v>181.8380211166871</v>
+        <v>178.4775815390208</v>
       </c>
       <c r="Q52">
-        <v>546.8380211166871</v>
+        <v>543.4775815390208</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1701807947765277</v>
+        <v>0.1723314713432688</v>
       </c>
       <c r="T52">
-        <v>2.87253567613228</v>
+        <v>2.922204880906901</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.08222758906422</v>
+        <v>2.041399597121784</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5832,22 +5832,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1128560509582017</v>
+        <v>0.1127652045281396</v>
       </c>
       <c r="C53">
-        <v>2093.748018643051</v>
+        <v>2037.502419639749</v>
       </c>
       <c r="D53">
-        <v>3001.113697407059</v>
+        <v>3005.185072497169</v>
       </c>
       <c r="E53">
-        <v>-2219.831730577185</v>
+        <v>-2159.514756483773</v>
       </c>
       <c r="F53">
-        <v>3076.165678764008</v>
+        <v>3136.48265285742</v>
       </c>
       <c r="G53">
         <v>2168.8</v>
@@ -5868,28 +5868,28 @@
         <v>476</v>
       </c>
       <c r="M53">
-        <v>233.1733584503118</v>
+        <v>237.7453850865925</v>
       </c>
       <c r="N53">
-        <v>242.8266415496882</v>
+        <v>238.2546149134075</v>
       </c>
       <c r="O53">
-        <v>64.34906001066737</v>
+        <v>63.137472952053</v>
       </c>
       <c r="P53">
-        <v>178.4775815390208</v>
+        <v>175.1171419613545</v>
       </c>
       <c r="Q53">
-        <v>543.4775815390208</v>
+        <v>540.1171419613545</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1723314713432688</v>
+        <v>0.1745717594336242</v>
       </c>
       <c r="T53">
-        <v>2.922204880906901</v>
+        <v>2.973943635880465</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.041399597121784</v>
+        <v>2.00214191256175</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5914,22 +5914,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1127652045281396</v>
+        <v>0.1182059680980775</v>
       </c>
       <c r="C54">
-        <v>2037.502419639749</v>
+        <v>1751.368404591701</v>
       </c>
       <c r="D54">
-        <v>3005.185072497169</v>
+        <v>2779.368031542533</v>
       </c>
       <c r="E54">
-        <v>-2159.514756483773</v>
+        <v>-2099.197782390361</v>
       </c>
       <c r="F54">
-        <v>3136.48265285742</v>
+        <v>3196.799626950832</v>
       </c>
       <c r="G54">
         <v>2168.8</v>
@@ -5950,45 +5950,45 @@
         <v>476</v>
       </c>
       <c r="M54">
-        <v>237.7453850865925</v>
+        <v>287.7119664255749</v>
       </c>
       <c r="N54">
-        <v>238.2546149134075</v>
+        <v>188.2880335744251</v>
       </c>
       <c r="O54">
-        <v>63.137472952053</v>
+        <v>49.89632889722266</v>
       </c>
       <c r="P54">
-        <v>175.1171419613545</v>
+        <v>138.3917046772025</v>
       </c>
       <c r="Q54">
-        <v>540.1171419613545</v>
+        <v>503.3917046772025</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1745717594336242</v>
+        <v>0.1769073789320797</v>
       </c>
       <c r="T54">
-        <v>2.973943635880465</v>
+        <v>3.027884040001841</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V54">
         <v>0.265</v>
       </c>
       <c r="W54">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.00214191256175</v>
+        <v>1.654432403051026</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5996,22 +5996,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1182059680980775</v>
+        <v>0.1182194916680153</v>
       </c>
       <c r="C55">
-        <v>1751.368404591701</v>
+        <v>1690.532413075051</v>
       </c>
       <c r="D55">
-        <v>2779.368031542533</v>
+        <v>2778.849014119296</v>
       </c>
       <c r="E55">
-        <v>-2099.197782390361</v>
+        <v>-2038.880808296949</v>
       </c>
       <c r="F55">
-        <v>3196.799626950832</v>
+        <v>3257.116601044244</v>
       </c>
       <c r="G55">
         <v>2168.8</v>
@@ -6032,28 +6032,28 @@
         <v>476</v>
       </c>
       <c r="M55">
-        <v>287.7119664255749</v>
+        <v>293.140494093982</v>
       </c>
       <c r="N55">
-        <v>188.2880335744251</v>
+        <v>182.859505906018</v>
       </c>
       <c r="O55">
-        <v>49.89632889722266</v>
+        <v>48.45776906509477</v>
       </c>
       <c r="P55">
-        <v>138.3917046772025</v>
+        <v>134.4017368409232</v>
       </c>
       <c r="Q55">
-        <v>503.3917046772025</v>
+        <v>499.4017368409233</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1769073789320797</v>
+        <v>0.1793445471043812</v>
       </c>
       <c r="T55">
-        <v>3.027884040001841</v>
+        <v>3.084169679085015</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.654432403051026</v>
+        <v>1.623794765957488</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6078,22 +6078,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1182194916680153</v>
+        <v>0.1182330152379532</v>
       </c>
       <c r="C56">
-        <v>1690.532413075051</v>
+        <v>1629.696615364181</v>
       </c>
       <c r="D56">
-        <v>2778.849014119296</v>
+        <v>2778.330190501837</v>
       </c>
       <c r="E56">
-        <v>-2038.880808296949</v>
+        <v>-1978.563834203537</v>
       </c>
       <c r="F56">
-        <v>3257.116601044244</v>
+        <v>3317.433575137656</v>
       </c>
       <c r="G56">
         <v>2168.8</v>
@@ -6114,28 +6114,28 @@
         <v>476</v>
       </c>
       <c r="M56">
-        <v>293.140494093982</v>
+        <v>298.569021762389</v>
       </c>
       <c r="N56">
-        <v>182.859505906018</v>
+        <v>177.430978237611</v>
       </c>
       <c r="O56">
-        <v>48.45776906509477</v>
+        <v>47.01920923296692</v>
       </c>
       <c r="P56">
-        <v>134.4017368409232</v>
+        <v>130.4117690046441</v>
       </c>
       <c r="Q56">
-        <v>499.4017368409233</v>
+        <v>495.411769004644</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1793445471043812</v>
+        <v>0.1818900338621182</v>
       </c>
       <c r="T56">
-        <v>3.084169679085015</v>
+        <v>3.142956902127441</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.623794765957488</v>
+        <v>1.594271224758262</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6160,22 +6160,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1182330152379532</v>
+        <v>0.1182465388078911</v>
       </c>
       <c r="C57">
-        <v>1629.696615364181</v>
+        <v>1568.861011350553</v>
       </c>
       <c r="D57">
-        <v>2778.330190501837</v>
+        <v>2777.811560581622</v>
       </c>
       <c r="E57">
-        <v>-1978.563834203537</v>
+        <v>-1918.246860110125</v>
       </c>
       <c r="F57">
-        <v>3317.433575137656</v>
+        <v>3377.750549231068</v>
       </c>
       <c r="G57">
         <v>2168.8</v>
@@ -6196,28 +6196,28 @@
         <v>476</v>
       </c>
       <c r="M57">
-        <v>298.569021762389</v>
+        <v>303.9975494307961</v>
       </c>
       <c r="N57">
-        <v>177.430978237611</v>
+        <v>172.0024505692039</v>
       </c>
       <c r="O57">
-        <v>47.01920923296692</v>
+        <v>45.58064940083902</v>
       </c>
       <c r="P57">
-        <v>130.4117690046441</v>
+        <v>126.4218011683648</v>
       </c>
       <c r="Q57">
-        <v>495.411769004644</v>
+        <v>491.4218011683648</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1818900338621182</v>
+        <v>0.1845512245633888</v>
       </c>
       <c r="T57">
-        <v>3.142956902127441</v>
+        <v>3.204416271671797</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.594271224758262</v>
+        <v>1.565802095744721</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6242,22 +6242,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1182465388078911</v>
+        <v>0.1182600623778289</v>
       </c>
       <c r="C58">
-        <v>1568.861011350553</v>
+        <v>1508.02560092572</v>
       </c>
       <c r="D58">
-        <v>2777.811560581622</v>
+        <v>2777.2931242502</v>
       </c>
       <c r="E58">
-        <v>-1918.246860110125</v>
+        <v>-1857.929886016713</v>
       </c>
       <c r="F58">
-        <v>3377.750549231068</v>
+        <v>3438.06752332448</v>
       </c>
       <c r="G58">
         <v>2168.8</v>
@@ -6278,28 +6278,28 @@
         <v>476</v>
       </c>
       <c r="M58">
-        <v>303.9975494307961</v>
+        <v>309.4260770992032</v>
       </c>
       <c r="N58">
-        <v>172.0024505692039</v>
+        <v>166.5739229007968</v>
       </c>
       <c r="O58">
-        <v>45.58064940083902</v>
+        <v>44.14208956871115</v>
       </c>
       <c r="P58">
-        <v>126.4218011683648</v>
+        <v>122.4318333320856</v>
       </c>
       <c r="Q58">
-        <v>491.4218011683648</v>
+        <v>487.4318333320856</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1845512245633888</v>
+        <v>0.1873361915763464</v>
       </c>
       <c r="T58">
-        <v>3.204416271671797</v>
+        <v>3.268734216543796</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.565802095744721</v>
+        <v>1.538331883538673</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6324,22 +6324,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1182600623778289</v>
+        <v>0.1182735859477668</v>
       </c>
       <c r="C59">
-        <v>1508.02560092572</v>
+        <v>1447.190383981307</v>
       </c>
       <c r="D59">
-        <v>2777.2931242502</v>
+        <v>2776.774881399199</v>
       </c>
       <c r="E59">
-        <v>-1857.929886016713</v>
+        <v>-1797.612911923301</v>
       </c>
       <c r="F59">
-        <v>3438.06752332448</v>
+        <v>3498.384497417892</v>
       </c>
       <c r="G59">
         <v>2168.8</v>
@@ -6360,28 +6360,28 @@
         <v>476</v>
       </c>
       <c r="M59">
-        <v>309.4260770992032</v>
+        <v>314.8546047676103</v>
       </c>
       <c r="N59">
-        <v>166.5739229007968</v>
+        <v>161.1453952323897</v>
       </c>
       <c r="O59">
-        <v>44.14208956871115</v>
+        <v>42.70352973658328</v>
       </c>
       <c r="P59">
-        <v>122.4318333320856</v>
+        <v>118.4418654958064</v>
       </c>
       <c r="Q59">
-        <v>487.4318333320856</v>
+        <v>483.4418654958064</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1873361915763464</v>
+        <v>0.1902537760661115</v>
       </c>
       <c r="T59">
-        <v>3.268734216543796</v>
+        <v>3.336114920695415</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.538331883538673</v>
+        <v>1.511808920029386</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6406,22 +6406,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1182735859477668</v>
+        <v>0.1459536543747166</v>
       </c>
       <c r="C60">
-        <v>1447.19038398131</v>
+        <v>619.43941855499</v>
       </c>
       <c r="D60">
-        <v>2776.774881399201</v>
+        <v>2009.340890066293</v>
       </c>
       <c r="E60">
-        <v>-1797.612911923301</v>
+        <v>-1737.295937829889</v>
       </c>
       <c r="F60">
-        <v>3498.384497417891</v>
+        <v>3558.701471511304</v>
       </c>
       <c r="G60">
         <v>2168.8</v>
@@ -6442,45 +6442,45 @@
         <v>476</v>
       </c>
       <c r="M60">
-        <v>314.8546047676102</v>
+        <v>522.4173760178594</v>
       </c>
       <c r="N60">
-        <v>161.1453952323898</v>
+        <v>-46.4173760178594</v>
       </c>
       <c r="O60">
-        <v>42.70352973658329</v>
+        <v>-12.30060464473274</v>
       </c>
       <c r="P60">
-        <v>118.4418654958065</v>
+        <v>-34.11677137312665</v>
       </c>
       <c r="Q60">
-        <v>483.4418654958065</v>
+        <v>330.8832286268733</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1902537760661114</v>
+        <v>0.1957427004036172</v>
       </c>
       <c r="T60">
-        <v>3.336114920695413</v>
+        <v>3.462879916942661</v>
       </c>
       <c r="U60">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.265</v>
+        <v>0.2414544496232219</v>
       </c>
       <c r="W60">
-        <v>0.06615</v>
+        <v>0.111354486795311</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.511808920029386</v>
+        <v>0.9111488665027241</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6488,22 +6488,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1459536543747166</v>
+        <v>0.1469636543747166</v>
       </c>
       <c r="C61">
-        <v>619.43941855499</v>
+        <v>539.0615410520413</v>
       </c>
       <c r="D61">
-        <v>2009.340890066293</v>
+        <v>1989.279986656756</v>
       </c>
       <c r="E61">
-        <v>-1737.295937829889</v>
+        <v>-1676.978963736477</v>
       </c>
       <c r="F61">
-        <v>3558.701471511304</v>
+        <v>3619.018445604715</v>
       </c>
       <c r="G61">
         <v>2168.8</v>
@@ -6524,37 +6524,37 @@
         <v>476</v>
       </c>
       <c r="M61">
-        <v>522.4173760178594</v>
+        <v>531.2719078147722</v>
       </c>
       <c r="N61">
-        <v>-46.4173760178594</v>
+        <v>-55.27190781477225</v>
       </c>
       <c r="O61">
-        <v>-12.30060464473274</v>
+        <v>-14.64705557091465</v>
       </c>
       <c r="P61">
-        <v>-34.11677137312665</v>
+        <v>-40.6248522438576</v>
       </c>
       <c r="Q61">
-        <v>330.8832286268733</v>
+        <v>324.3751477561424</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1957427004036172</v>
+        <v>0.1994912679137077</v>
       </c>
       <c r="T61">
-        <v>3.462879916942661</v>
+        <v>3.549451914866228</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2414544496232219</v>
+        <v>0.2374302087961682</v>
       </c>
       <c r="W61">
-        <v>0.111354486795311</v>
+        <v>0.1119452453487225</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9111488665027241</v>
+        <v>0.8959630520610121</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6570,22 +6570,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1469636543747166</v>
+        <v>0.1479736543747166</v>
       </c>
       <c r="C62">
-        <v>539.0615410520413</v>
+        <v>459.080272881853</v>
       </c>
       <c r="D62">
-        <v>1989.279986656756</v>
+        <v>1969.61569257998</v>
       </c>
       <c r="E62">
-        <v>-1676.978963736477</v>
+        <v>-1616.661989643065</v>
       </c>
       <c r="F62">
-        <v>3619.018445604715</v>
+        <v>3679.335419698128</v>
       </c>
       <c r="G62">
         <v>2168.8</v>
@@ -6606,37 +6606,37 @@
         <v>476</v>
       </c>
       <c r="M62">
-        <v>531.2719078147722</v>
+        <v>540.1264396116852</v>
       </c>
       <c r="N62">
-        <v>-55.27190781477225</v>
+        <v>-64.12643961168521</v>
       </c>
       <c r="O62">
-        <v>-14.64705557091465</v>
+        <v>-16.99350649709658</v>
       </c>
       <c r="P62">
-        <v>-40.6248522438576</v>
+        <v>-47.13293311458863</v>
       </c>
       <c r="Q62">
-        <v>324.3751477561424</v>
+        <v>317.8670668854114</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1994912679137077</v>
+        <v>0.2034320696550848</v>
       </c>
       <c r="T62">
-        <v>3.549451914866228</v>
+        <v>3.6404635024269</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2374302087961682</v>
+        <v>0.233537910291313</v>
       </c>
       <c r="W62">
-        <v>0.1119452453487225</v>
+        <v>0.1125166347692353</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8959630520610121</v>
+        <v>0.8812751331747658</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6652,22 +6652,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1479736543747166</v>
+        <v>0.1489836543747166</v>
       </c>
       <c r="C63">
-        <v>459.080272881853</v>
+        <v>379.4839675652852</v>
       </c>
       <c r="D63">
-        <v>1969.61569257998</v>
+        <v>1950.336361356825</v>
       </c>
       <c r="E63">
-        <v>-1616.661989643065</v>
+        <v>-1556.345015549653</v>
       </c>
       <c r="F63">
-        <v>3679.335419698128</v>
+        <v>3739.652393791539</v>
       </c>
       <c r="G63">
         <v>2168.8</v>
@@ -6688,37 +6688,37 @@
         <v>476</v>
       </c>
       <c r="M63">
-        <v>540.1264396116852</v>
+        <v>548.9809714085981</v>
       </c>
       <c r="N63">
-        <v>-64.12643961168521</v>
+        <v>-72.98097140859807</v>
       </c>
       <c r="O63">
-        <v>-16.99350649709658</v>
+        <v>-19.33995742327849</v>
       </c>
       <c r="P63">
-        <v>-47.13293311458863</v>
+        <v>-53.64101398531957</v>
       </c>
       <c r="Q63">
-        <v>317.8670668854114</v>
+        <v>311.3589860146805</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2034320696550848</v>
+        <v>0.2075802820144291</v>
       </c>
       <c r="T63">
-        <v>3.6404635024269</v>
+        <v>3.736265173543398</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.233537910291313</v>
+        <v>0.2297711698027434</v>
       </c>
       <c r="W63">
-        <v>0.1125166347692353</v>
+        <v>0.1130695922729573</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8812751331747658</v>
+        <v>0.86706101812356</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6734,22 +6734,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1489836543747166</v>
+        <v>0.1499936543747166</v>
       </c>
       <c r="C64">
-        <v>379.4839675652852</v>
+        <v>300.2614302032493</v>
       </c>
       <c r="D64">
-        <v>1950.336361356825</v>
+        <v>1931.4307980882</v>
       </c>
       <c r="E64">
-        <v>-1556.345015549653</v>
+        <v>-1496.028041456242</v>
       </c>
       <c r="F64">
-        <v>3739.652393791539</v>
+        <v>3799.969367884951</v>
       </c>
       <c r="G64">
         <v>2168.8</v>
@@ -6770,37 +6770,37 @@
         <v>476</v>
       </c>
       <c r="M64">
-        <v>548.9809714085981</v>
+        <v>557.8355032055109</v>
       </c>
       <c r="N64">
-        <v>-72.98097140859807</v>
+        <v>-81.83550320551092</v>
       </c>
       <c r="O64">
-        <v>-19.33995742327849</v>
+        <v>-21.68640834946039</v>
       </c>
       <c r="P64">
-        <v>-53.64101398531957</v>
+        <v>-60.14909485605052</v>
       </c>
       <c r="Q64">
-        <v>311.3589860146805</v>
+        <v>304.8509051439495</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2075802820144291</v>
+        <v>0.2119527220688732</v>
       </c>
       <c r="T64">
-        <v>3.736265173543398</v>
+        <v>3.837245313368895</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2297711698027434</v>
+        <v>0.226124008377303</v>
       </c>
       <c r="W64">
-        <v>0.1130695922729573</v>
+        <v>0.1136049955702119</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.86706101812356</v>
+        <v>0.8532981448200114</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6816,22 +6816,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1499936543747166</v>
+        <v>0.1510036543747166</v>
       </c>
       <c r="C65">
-        <v>300.2614302032493</v>
+        <v>221.4018957998987</v>
       </c>
       <c r="D65">
-        <v>1931.4307980882</v>
+        <v>1912.888237778262</v>
       </c>
       <c r="E65">
-        <v>-1496.028041456242</v>
+        <v>-1435.711067362829</v>
       </c>
       <c r="F65">
-        <v>3799.969367884951</v>
+        <v>3860.286341978363</v>
       </c>
       <c r="G65">
         <v>2168.8</v>
@@ -6852,37 +6852,37 @@
         <v>476</v>
       </c>
       <c r="M65">
-        <v>557.8355032055109</v>
+        <v>566.6900350024238</v>
       </c>
       <c r="N65">
-        <v>-81.83550320551092</v>
+        <v>-90.69003500242377</v>
       </c>
       <c r="O65">
-        <v>-21.68640834946039</v>
+        <v>-24.0328592756423</v>
       </c>
       <c r="P65">
-        <v>-60.14909485605052</v>
+        <v>-66.65717572678147</v>
       </c>
       <c r="Q65">
-        <v>304.8509051439495</v>
+        <v>298.3428242732185</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2119527220688732</v>
+        <v>0.2165680754596752</v>
       </c>
       <c r="T65">
-        <v>3.837245313368895</v>
+        <v>3.943835460962475</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.226124008377303</v>
+        <v>0.2225908207464077</v>
       </c>
       <c r="W65">
-        <v>0.1136049955702119</v>
+        <v>0.1141236675144274</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8532981448200114</v>
+        <v>0.8399653613071988</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6898,22 +6898,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1510036543747166</v>
+        <v>0.1520136543747166</v>
       </c>
       <c r="C66">
-        <v>221.4018957998987</v>
+        <v>142.8950088225934</v>
       </c>
       <c r="D66">
-        <v>1912.888237778262</v>
+        <v>1894.698324894368</v>
       </c>
       <c r="E66">
-        <v>-1435.711067362829</v>
+        <v>-1375.394093269418</v>
       </c>
       <c r="F66">
-        <v>3860.286341978363</v>
+        <v>3920.603316071775</v>
       </c>
       <c r="G66">
         <v>2168.8</v>
@@ -6934,37 +6934,37 @@
         <v>476</v>
       </c>
       <c r="M66">
-        <v>566.6900350024238</v>
+        <v>575.5445667993366</v>
       </c>
       <c r="N66">
-        <v>-90.69003500242377</v>
+        <v>-99.54456679933662</v>
       </c>
       <c r="O66">
-        <v>-24.0328592756423</v>
+        <v>-26.37931020182421</v>
       </c>
       <c r="P66">
-        <v>-66.65717572678147</v>
+        <v>-73.16525659751241</v>
       </c>
       <c r="Q66">
-        <v>298.3428242732185</v>
+        <v>291.8347434024876</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2165680754596752</v>
+        <v>0.2214471633299516</v>
       </c>
       <c r="T66">
-        <v>3.943835460962475</v>
+        <v>4.056516474132832</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2225908207464077</v>
+        <v>0.2191663465810783</v>
       </c>
       <c r="W66">
-        <v>0.1141236675144274</v>
+        <v>0.1146263803218977</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8399653613071988</v>
+        <v>0.8270428172870881</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6980,22 +6980,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1520136543747166</v>
+        <v>0.1530236543747166</v>
       </c>
       <c r="C67">
-        <v>142.8950088225934</v>
+        <v>64.73080391707254</v>
       </c>
       <c r="D67">
-        <v>1894.698324894368</v>
+        <v>1876.85109408226</v>
       </c>
       <c r="E67">
-        <v>-1375.394093269418</v>
+        <v>-1315.077119176005</v>
       </c>
       <c r="F67">
-        <v>3920.603316071775</v>
+        <v>3980.920290165187</v>
       </c>
       <c r="G67">
         <v>2168.8</v>
@@ -7016,37 +7016,37 @@
         <v>476</v>
       </c>
       <c r="M67">
-        <v>575.5445667993366</v>
+        <v>584.3990985962496</v>
       </c>
       <c r="N67">
-        <v>-99.54456679933662</v>
+        <v>-108.3990985962496</v>
       </c>
       <c r="O67">
-        <v>-26.37931020182421</v>
+        <v>-28.72576112800614</v>
       </c>
       <c r="P67">
-        <v>-73.16525659751241</v>
+        <v>-79.67333746824345</v>
       </c>
       <c r="Q67">
-        <v>291.8347434024876</v>
+        <v>285.3266625317565</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2214471633299516</v>
+        <v>0.2266132563690678</v>
       </c>
       <c r="T67">
-        <v>4.056516474132832</v>
+        <v>4.175825782195562</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2191663465810783</v>
+        <v>0.2158456443601529</v>
       </c>
       <c r="W67">
-        <v>0.1146263803218977</v>
+        <v>0.1151138594079296</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8270428172870881</v>
+        <v>0.8145118655100108</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7062,22 +7062,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1530236543747166</v>
+        <v>0.1540336543747166</v>
       </c>
       <c r="C68">
-        <v>64.73080391707254</v>
+        <v>-13.10031229760853</v>
       </c>
       <c r="D68">
-        <v>1876.85109408226</v>
+        <v>1859.336951960991</v>
       </c>
       <c r="E68">
-        <v>-1315.077119176005</v>
+        <v>-1254.760145082594</v>
       </c>
       <c r="F68">
-        <v>3980.920290165187</v>
+        <v>4041.237264258599</v>
       </c>
       <c r="G68">
         <v>2168.8</v>
@@ -7098,37 +7098,37 @@
         <v>476</v>
       </c>
       <c r="M68">
-        <v>584.3990985962496</v>
+        <v>593.2536303931624</v>
       </c>
       <c r="N68">
-        <v>-108.3990985962496</v>
+        <v>-117.2536303931624</v>
       </c>
       <c r="O68">
-        <v>-28.72576112800614</v>
+        <v>-31.07221205418805</v>
       </c>
       <c r="P68">
-        <v>-79.67333746824345</v>
+        <v>-86.1814183389744</v>
       </c>
       <c r="Q68">
-        <v>285.3266625317565</v>
+        <v>278.8185816610256</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2266132563690678</v>
+        <v>0.2320924459560093</v>
       </c>
       <c r="T68">
-        <v>4.175825782195562</v>
+        <v>4.302365957413611</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2158456443601529</v>
+        <v>0.2126240675786581</v>
       </c>
       <c r="W68">
-        <v>0.1151138594079296</v>
+        <v>0.115586786879453</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8145118655100108</v>
+        <v>0.8023549719949361</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7144,22 +7144,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1540336543747166</v>
+        <v>0.1945101007551843</v>
       </c>
       <c r="C69">
-        <v>-13.10031229760853</v>
+        <v>-579.4982590827672</v>
       </c>
       <c r="D69">
-        <v>1859.336951960991</v>
+        <v>1353.255979269244</v>
       </c>
       <c r="E69">
-        <v>-1254.760145082594</v>
+        <v>-1194.443170989181</v>
       </c>
       <c r="F69">
-        <v>4041.237264258599</v>
+        <v>4101.554238352011</v>
       </c>
       <c r="G69">
         <v>2168.8</v>
@@ -7180,45 +7180,45 @@
         <v>476</v>
       </c>
       <c r="M69">
-        <v>593.2536303931624</v>
+        <v>823.5920910610839</v>
       </c>
       <c r="N69">
-        <v>-117.2536303931624</v>
+        <v>-347.5920910610839</v>
       </c>
       <c r="O69">
-        <v>-31.07221205418805</v>
+        <v>-92.11190413118725</v>
       </c>
       <c r="P69">
-        <v>-86.1814183389744</v>
+        <v>-255.4801869298967</v>
       </c>
       <c r="Q69">
-        <v>278.8185816610256</v>
+        <v>109.5198130701033</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2320924459560093</v>
+        <v>0.2464967298310962</v>
       </c>
       <c r="T69">
-        <v>4.302365957413611</v>
+        <v>4.635028402565733</v>
       </c>
       <c r="U69">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.2126240675786581</v>
+        <v>0.1531583430305725</v>
       </c>
       <c r="W69">
-        <v>0.115586786879453</v>
+        <v>0.170045804719461</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.8023549719949361</v>
+        <v>0.5779560114361226</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7226,22 +7226,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1945101007551843</v>
+        <v>0.1960601007551843</v>
       </c>
       <c r="C70">
-        <v>-579.4982590827672</v>
+        <v>-653.7746725571278</v>
       </c>
       <c r="D70">
-        <v>1353.255979269244</v>
+        <v>1339.296539888295</v>
       </c>
       <c r="E70">
-        <v>-1194.443170989181</v>
+        <v>-1134.12619689577</v>
       </c>
       <c r="F70">
-        <v>4101.554238352011</v>
+        <v>4161.871212445423</v>
       </c>
       <c r="G70">
         <v>2168.8</v>
@@ -7262,37 +7262,37 @@
         <v>476</v>
       </c>
       <c r="M70">
-        <v>823.5920910610839</v>
+        <v>835.703739459041</v>
       </c>
       <c r="N70">
-        <v>-347.5920910610839</v>
+        <v>-359.703739459041</v>
       </c>
       <c r="O70">
-        <v>-92.11190413118725</v>
+        <v>-95.32149095664587</v>
       </c>
       <c r="P70">
-        <v>-255.4801869298967</v>
+        <v>-264.3822485023951</v>
       </c>
       <c r="Q70">
-        <v>109.5198130701033</v>
+        <v>100.6177514976049</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2464967298310962</v>
+        <v>0.2529708178901639</v>
       </c>
       <c r="T70">
-        <v>4.635028402565733</v>
+        <v>4.78454544780979</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1531583430305725</v>
+        <v>0.1509386568996947</v>
       </c>
       <c r="W70">
-        <v>0.170045804719461</v>
+        <v>0.1704915176945413</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5779560114361226</v>
+        <v>0.5695798373573383</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7308,22 +7308,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1960601007551843</v>
+        <v>0.1976101007551843</v>
       </c>
       <c r="C71">
-        <v>-653.7746725571278</v>
+        <v>-727.7660308087757</v>
       </c>
       <c r="D71">
-        <v>1339.296539888295</v>
+        <v>1325.622155730059</v>
       </c>
       <c r="E71">
-        <v>-1134.12619689577</v>
+        <v>-1073.809222802358</v>
       </c>
       <c r="F71">
-        <v>4161.871212445423</v>
+        <v>4222.188186538835</v>
       </c>
       <c r="G71">
         <v>2168.8</v>
@@ -7344,37 +7344,37 @@
         <v>476</v>
       </c>
       <c r="M71">
-        <v>835.703739459041</v>
+        <v>847.8153878569981</v>
       </c>
       <c r="N71">
-        <v>-359.703739459041</v>
+        <v>-371.8153878569981</v>
       </c>
       <c r="O71">
-        <v>-95.32149095664587</v>
+        <v>-98.5310777821045</v>
       </c>
       <c r="P71">
-        <v>-264.3822485023951</v>
+        <v>-273.2843100748936</v>
       </c>
       <c r="Q71">
-        <v>100.6177514976049</v>
+        <v>91.7156899251064</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2529708178901639</v>
+        <v>0.259876511819836</v>
       </c>
       <c r="T71">
-        <v>4.78454544780979</v>
+        <v>4.944030296070116</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1509386568996947</v>
+        <v>0.1487823903725562</v>
       </c>
       <c r="W71">
-        <v>0.1704915176945413</v>
+        <v>0.1709244960131907</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5695798373573383</v>
+        <v>0.5614429825379478</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7390,22 +7390,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1976101007551843</v>
+        <v>0.1991601007551843</v>
       </c>
       <c r="C72">
-        <v>-727.7660308087757</v>
+        <v>-801.4809769383546</v>
       </c>
       <c r="D72">
-        <v>1325.622155730059</v>
+        <v>1312.224183693893</v>
       </c>
       <c r="E72">
-        <v>-1073.809222802358</v>
+        <v>-1013.492248708945</v>
       </c>
       <c r="F72">
-        <v>4222.188186538835</v>
+        <v>4282.505160632248</v>
       </c>
       <c r="G72">
         <v>2168.8</v>
@@ -7426,37 +7426,37 @@
         <v>476</v>
       </c>
       <c r="M72">
-        <v>847.8153878569981</v>
+        <v>859.9270362549554</v>
       </c>
       <c r="N72">
-        <v>-371.8153878569981</v>
+        <v>-383.9270362549554</v>
       </c>
       <c r="O72">
-        <v>-98.5310777821045</v>
+        <v>-101.7406646075632</v>
       </c>
       <c r="P72">
-        <v>-273.2843100748936</v>
+        <v>-282.1863716473922</v>
       </c>
       <c r="Q72">
-        <v>91.7156899251064</v>
+        <v>82.81362835260779</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.259876511819836</v>
+        <v>0.2672584605032786</v>
       </c>
       <c r="T72">
-        <v>4.944030296070116</v>
+        <v>5.114514099382879</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1487823903725562</v>
+        <v>0.1466868637475906</v>
       </c>
       <c r="W72">
-        <v>0.1709244960131907</v>
+        <v>0.1713452777594838</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5614429825379478</v>
+        <v>0.5535353348965681</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7472,22 +7472,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1991601007551843</v>
+        <v>0.2007101007551843</v>
       </c>
       <c r="C73">
-        <v>-801.4809769383528</v>
+        <v>-874.9278081218454</v>
       </c>
       <c r="D73">
-        <v>1312.224183693894</v>
+        <v>1299.094326603813</v>
       </c>
       <c r="E73">
-        <v>-1013.492248708946</v>
+        <v>-953.1752746155344</v>
       </c>
       <c r="F73">
-        <v>4282.505160632247</v>
+        <v>4342.822134725659</v>
       </c>
       <c r="G73">
         <v>2168.8</v>
@@ -7508,37 +7508,37 @@
         <v>476</v>
       </c>
       <c r="M73">
-        <v>859.9270362549552</v>
+        <v>872.0386846529123</v>
       </c>
       <c r="N73">
-        <v>-383.9270362549552</v>
+        <v>-396.0386846529123</v>
       </c>
       <c r="O73">
-        <v>-101.7406646075631</v>
+        <v>-104.9502514330217</v>
       </c>
       <c r="P73">
-        <v>-282.186371647392</v>
+        <v>-291.0884332198905</v>
       </c>
       <c r="Q73">
-        <v>82.81362835260796</v>
+        <v>73.91156678010952</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2672584605032785</v>
+        <v>0.2751676912355385</v>
       </c>
       <c r="T73">
-        <v>5.114514099382876</v>
+        <v>5.29717531721798</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1466868637475906</v>
+        <v>0.1446495461955407</v>
       </c>
       <c r="W73">
-        <v>0.1713452777594838</v>
+        <v>0.1717543711239354</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5535353348965683</v>
+        <v>0.545847344134116</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7554,22 +7554,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2007101007551843</v>
+        <v>0.2022601007551843</v>
       </c>
       <c r="C74">
-        <v>-874.9278081218454</v>
+        <v>-948.1144927453988</v>
       </c>
       <c r="D74">
-        <v>1299.094326603813</v>
+        <v>1286.224616073672</v>
       </c>
       <c r="E74">
-        <v>-953.1752746155344</v>
+        <v>-892.8583005221226</v>
       </c>
       <c r="F74">
-        <v>4342.822134725659</v>
+        <v>4403.13910881907</v>
       </c>
       <c r="G74">
         <v>2168.8</v>
@@ -7590,37 +7590,37 @@
         <v>476</v>
       </c>
       <c r="M74">
-        <v>872.0386846529123</v>
+        <v>884.1503330508693</v>
       </c>
       <c r="N74">
-        <v>-396.0386846529123</v>
+        <v>-408.1503330508693</v>
       </c>
       <c r="O74">
-        <v>-104.9502514330217</v>
+        <v>-108.1598382584804</v>
       </c>
       <c r="P74">
-        <v>-291.0884332198905</v>
+        <v>-299.990494792389</v>
       </c>
       <c r="Q74">
-        <v>73.91156678010952</v>
+        <v>65.00950520761103</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2751676912355385</v>
+        <v>0.2836627909109288</v>
       </c>
       <c r="T74">
-        <v>5.29717531721798</v>
+        <v>5.49336699563346</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1446495461955407</v>
+        <v>0.1426680455627251</v>
       </c>
       <c r="W74">
-        <v>0.1717543711239354</v>
+        <v>0.1721522564510048</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.545847344134116</v>
+        <v>0.5383699832555664</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7636,22 +7636,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2022601007551843</v>
+        <v>0.2038101007551843</v>
       </c>
       <c r="C75">
-        <v>-948.1144927453988</v>
+        <v>-1021.04868653164</v>
       </c>
       <c r="D75">
-        <v>1286.224616073672</v>
+        <v>1273.607396380843</v>
       </c>
       <c r="E75">
-        <v>-892.8583005221226</v>
+        <v>-832.5413264287099</v>
       </c>
       <c r="F75">
-        <v>4403.13910881907</v>
+        <v>4463.456082912483</v>
       </c>
       <c r="G75">
         <v>2168.8</v>
@@ -7672,37 +7672,37 @@
         <v>476</v>
       </c>
       <c r="M75">
-        <v>884.1503330508693</v>
+        <v>896.2619814488266</v>
       </c>
       <c r="N75">
-        <v>-408.1503330508693</v>
+        <v>-420.2619814488266</v>
       </c>
       <c r="O75">
-        <v>-108.1598382584804</v>
+        <v>-111.3694250839391</v>
       </c>
       <c r="P75">
-        <v>-299.990494792389</v>
+        <v>-308.8925563648876</v>
       </c>
       <c r="Q75">
-        <v>65.00950520761103</v>
+        <v>56.10744363511242</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2836627909109288</v>
+        <v>0.2928113597921184</v>
       </c>
       <c r="T75">
-        <v>5.49336699563346</v>
+        <v>5.704650341619362</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1426680455627251</v>
+        <v>0.1407400990010666</v>
       </c>
       <c r="W75">
-        <v>0.1721522564510048</v>
+        <v>0.1725393881205858</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5383699832555664</v>
+        <v>0.5310947132115722</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7718,22 +7718,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2038101007551843</v>
+        <v>0.2053601007551843</v>
       </c>
       <c r="C76">
-        <v>-1021.04868653164</v>
+        <v>-1093.737747726069</v>
       </c>
       <c r="D76">
-        <v>1273.607396380843</v>
+        <v>1261.235309279825</v>
       </c>
       <c r="E76">
-        <v>-832.5413264287099</v>
+        <v>-772.2243523352981</v>
       </c>
       <c r="F76">
-        <v>4463.456082912483</v>
+        <v>4523.773057005895</v>
       </c>
       <c r="G76">
         <v>2168.8</v>
@@ -7754,37 +7754,37 @@
         <v>476</v>
       </c>
       <c r="M76">
-        <v>896.2619814488266</v>
+        <v>908.3736298467837</v>
       </c>
       <c r="N76">
-        <v>-420.2619814488266</v>
+        <v>-432.3736298467837</v>
       </c>
       <c r="O76">
-        <v>-111.3694250839391</v>
+        <v>-114.5790119093977</v>
       </c>
       <c r="P76">
-        <v>-308.8925563648876</v>
+        <v>-317.794617937386</v>
       </c>
       <c r="Q76">
-        <v>56.10744363511242</v>
+        <v>47.20538206261398</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2928113597921184</v>
+        <v>0.3026918141838031</v>
       </c>
       <c r="T76">
-        <v>5.704650341619362</v>
+        <v>5.932836355284137</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1407400990010666</v>
+        <v>0.1388635643477191</v>
       </c>
       <c r="W76">
-        <v>0.1725393881205858</v>
+        <v>0.172916196278978</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5310947132115722</v>
+        <v>0.5240134503687512</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7800,22 +7800,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2053601007551843</v>
+        <v>0.2069101007551843</v>
       </c>
       <c r="C77">
-        <v>-1093.737747726069</v>
+        <v>-1166.188751406828</v>
       </c>
       <c r="D77">
-        <v>1261.235309279825</v>
+        <v>1249.101279692479</v>
       </c>
       <c r="E77">
-        <v>-772.2243523352981</v>
+        <v>-711.9073782418864</v>
       </c>
       <c r="F77">
-        <v>4523.773057005895</v>
+        <v>4584.090031099307</v>
       </c>
       <c r="G77">
         <v>2168.8</v>
@@ -7836,37 +7836,37 @@
         <v>476</v>
       </c>
       <c r="M77">
-        <v>908.3736298467837</v>
+        <v>920.4852782447408</v>
       </c>
       <c r="N77">
-        <v>-432.3736298467837</v>
+        <v>-444.4852782447408</v>
       </c>
       <c r="O77">
-        <v>-114.5790119093977</v>
+        <v>-117.7885987348563</v>
       </c>
       <c r="P77">
-        <v>-317.794617937386</v>
+        <v>-326.6966795098845</v>
       </c>
       <c r="Q77">
-        <v>47.20538206261398</v>
+        <v>38.30332049011554</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3026918141838031</v>
+        <v>0.313395639774795</v>
       </c>
       <c r="T77">
-        <v>5.932836355284137</v>
+        <v>6.180037870087643</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1388635643477191</v>
+        <v>0.1370364121852491</v>
       </c>
       <c r="W77">
-        <v>0.172916196278978</v>
+        <v>0.173283088433202</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5240134503687512</v>
+        <v>0.5171185365481098</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7882,22 +7882,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2069101007551843</v>
+        <v>0.2084601007551843</v>
       </c>
       <c r="C78">
-        <v>-1166.188751406828</v>
+        <v>-1238.408502976305</v>
       </c>
       <c r="D78">
-        <v>1249.101279692479</v>
+        <v>1237.198502216414</v>
       </c>
       <c r="E78">
-        <v>-711.9073782418864</v>
+        <v>-651.5904041484746</v>
       </c>
       <c r="F78">
-        <v>4584.090031099307</v>
+        <v>4644.407005192718</v>
       </c>
       <c r="G78">
         <v>2168.8</v>
@@ -7918,37 +7918,37 @@
         <v>476</v>
       </c>
       <c r="M78">
-        <v>920.4852782447408</v>
+        <v>932.5969266426979</v>
       </c>
       <c r="N78">
-        <v>-444.4852782447408</v>
+        <v>-456.5969266426979</v>
       </c>
       <c r="O78">
-        <v>-117.7885987348563</v>
+        <v>-120.998185560315</v>
       </c>
       <c r="P78">
-        <v>-326.6966795098845</v>
+        <v>-335.598741082383</v>
       </c>
       <c r="Q78">
-        <v>38.30332049011554</v>
+        <v>29.40125891761704</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.313395639774795</v>
+        <v>0.3250302328084817</v>
       </c>
       <c r="T78">
-        <v>6.180037870087643</v>
+        <v>6.448735168787106</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1370364121852491</v>
+        <v>0.1352567185205056</v>
       </c>
       <c r="W78">
-        <v>0.173283088433202</v>
+        <v>0.1736404509210825</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5171185365481098</v>
+        <v>0.5104027113981344</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7964,22 +7964,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2084601007551843</v>
+        <v>0.2100101007551843</v>
       </c>
       <c r="C79">
-        <v>-1238.408502976305</v>
+        <v>-1310.403550888661</v>
       </c>
       <c r="D79">
-        <v>1237.198502216414</v>
+        <v>1225.520428397469</v>
       </c>
       <c r="E79">
-        <v>-651.5904041484746</v>
+        <v>-591.2734300550628</v>
       </c>
       <c r="F79">
-        <v>4644.407005192718</v>
+        <v>4704.72397928613</v>
       </c>
       <c r="G79">
         <v>2168.8</v>
@@ -8000,37 +8000,37 @@
         <v>476</v>
       </c>
       <c r="M79">
-        <v>932.5969266426979</v>
+        <v>944.708575040655</v>
       </c>
       <c r="N79">
-        <v>-456.5969266426979</v>
+        <v>-468.708575040655</v>
       </c>
       <c r="O79">
-        <v>-120.998185560315</v>
+        <v>-124.2077723857736</v>
       </c>
       <c r="P79">
-        <v>-335.598741082383</v>
+        <v>-344.5008026548814</v>
       </c>
       <c r="Q79">
-        <v>29.40125891761704</v>
+        <v>20.4991973451186</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3250302328084817</v>
+        <v>0.3377225161179581</v>
       </c>
       <c r="T79">
-        <v>6.448735168787106</v>
+        <v>6.741859494641066</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1352567185205056</v>
+        <v>0.133522658026653</v>
       </c>
       <c r="W79">
-        <v>0.1736404509210825</v>
+        <v>0.1739886502682481</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5104027113981344</v>
+        <v>0.5038590868930301</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8046,22 +8046,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2100101007551843</v>
+        <v>0.2403183250430965</v>
       </c>
       <c r="C80">
-        <v>-1310.403550888661</v>
+        <v>-1561.670904618848</v>
       </c>
       <c r="D80">
-        <v>1225.520428397469</v>
+        <v>1034.570048760694</v>
       </c>
       <c r="E80">
-        <v>-591.2734300550628</v>
+        <v>-530.9564559616501</v>
       </c>
       <c r="F80">
-        <v>4704.72397928613</v>
+        <v>4765.040953379543</v>
       </c>
       <c r="G80">
         <v>2168.8</v>
@@ -8082,45 +8082,45 @@
         <v>476</v>
       </c>
       <c r="M80">
-        <v>944.708575040655</v>
+        <v>1123.596656806896</v>
       </c>
       <c r="N80">
-        <v>-468.708575040655</v>
+        <v>-647.5966568068961</v>
       </c>
       <c r="O80">
-        <v>-124.2077723857736</v>
+        <v>-171.6131140538275</v>
       </c>
       <c r="P80">
-        <v>-344.5008026548814</v>
+        <v>-475.9835427530687</v>
       </c>
       <c r="Q80">
-        <v>20.4991973451186</v>
+        <v>-110.9835427530687</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3377225161179581</v>
+        <v>0.3569008468279188</v>
       </c>
       <c r="T80">
-        <v>6.741859494641066</v>
+        <v>7.184777063000435</v>
       </c>
       <c r="U80">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.133522658026653</v>
+        <v>0.1122644849785084</v>
       </c>
       <c r="W80">
-        <v>0.1739886502682481</v>
+        <v>0.2093280344420677</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5038590868930301</v>
+        <v>0.4236395659566353</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8128,22 +8128,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2403183250430965</v>
+        <v>0.2422183250430965</v>
       </c>
       <c r="C81">
-        <v>-1561.670904618848</v>
+        <v>-1631.995514670942</v>
       </c>
       <c r="D81">
-        <v>1034.570048760694</v>
+        <v>1024.562412802012</v>
       </c>
       <c r="E81">
-        <v>-530.9564559616501</v>
+        <v>-470.6394818682384</v>
       </c>
       <c r="F81">
-        <v>4765.040953379543</v>
+        <v>4825.357927472955</v>
       </c>
       <c r="G81">
         <v>2168.8</v>
@@ -8164,37 +8164,37 @@
         <v>476</v>
       </c>
       <c r="M81">
-        <v>1123.596656806896</v>
+        <v>1137.819399298123</v>
       </c>
       <c r="N81">
-        <v>-647.5966568068961</v>
+        <v>-661.8193992981228</v>
       </c>
       <c r="O81">
-        <v>-171.6131140538275</v>
+        <v>-175.3821408140026</v>
       </c>
       <c r="P81">
-        <v>-475.9835427530687</v>
+        <v>-486.4372584841202</v>
       </c>
       <c r="Q81">
-        <v>-110.9835427530687</v>
+        <v>-121.4372584841202</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3569008468279188</v>
+        <v>0.3724558891693148</v>
       </c>
       <c r="T81">
-        <v>7.184777063000435</v>
+        <v>7.544015916150458</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1122644849785084</v>
+        <v>0.110861178916277</v>
       </c>
       <c r="W81">
-        <v>0.2093280344420677</v>
+        <v>0.2096589340115419</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4236395659566353</v>
+        <v>0.4183440713821773</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8210,22 +8210,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2422183250430965</v>
+        <v>0.2441183250430964</v>
       </c>
       <c r="C82">
-        <v>-1631.995514670942</v>
+        <v>-1702.128367271298</v>
       </c>
       <c r="D82">
-        <v>1024.562412802012</v>
+        <v>1014.746534295068</v>
       </c>
       <c r="E82">
-        <v>-470.6394818682384</v>
+        <v>-410.3225077748266</v>
       </c>
       <c r="F82">
-        <v>4825.357927472955</v>
+        <v>4885.674901566366</v>
       </c>
       <c r="G82">
         <v>2168.8</v>
@@ -8246,37 +8246,37 @@
         <v>476</v>
       </c>
       <c r="M82">
-        <v>1137.819399298123</v>
+        <v>1152.042141789349</v>
       </c>
       <c r="N82">
-        <v>-661.8193992981228</v>
+        <v>-676.0421417893492</v>
       </c>
       <c r="O82">
-        <v>-175.3821408140026</v>
+        <v>-179.1511675741775</v>
       </c>
       <c r="P82">
-        <v>-486.4372584841202</v>
+        <v>-496.8909742151717</v>
       </c>
       <c r="Q82">
-        <v>-121.4372584841202</v>
+        <v>-131.8909742151717</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3724558891693148</v>
+        <v>0.3896483043887524</v>
       </c>
       <c r="T82">
-        <v>7.544015916150458</v>
+        <v>7.941069385421534</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.110861178916277</v>
+        <v>0.1094925223864464</v>
       </c>
       <c r="W82">
-        <v>0.2096589340115419</v>
+        <v>0.2099816632212759</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4183440713821773</v>
+        <v>0.4131793297601751</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8292,22 +8292,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2441183250430964</v>
+        <v>0.2460183250430965</v>
       </c>
       <c r="C83">
-        <v>-1702.128367271298</v>
+        <v>-1772.07492154797</v>
       </c>
       <c r="D83">
-        <v>1014.746534295068</v>
+        <v>1005.116954111808</v>
       </c>
       <c r="E83">
-        <v>-410.3225077748266</v>
+        <v>-350.0055336814148</v>
       </c>
       <c r="F83">
-        <v>4885.674901566366</v>
+        <v>4945.991875659778</v>
       </c>
       <c r="G83">
         <v>2168.8</v>
@@ -8328,37 +8328,37 @@
         <v>476</v>
       </c>
       <c r="M83">
-        <v>1152.042141789349</v>
+        <v>1166.264884280576</v>
       </c>
       <c r="N83">
-        <v>-676.0421417893492</v>
+        <v>-690.2648842805756</v>
       </c>
       <c r="O83">
-        <v>-179.1511675741775</v>
+        <v>-182.9201943343525</v>
       </c>
       <c r="P83">
-        <v>-496.8909742151717</v>
+        <v>-507.3446899462231</v>
       </c>
       <c r="Q83">
-        <v>-131.8909742151717</v>
+        <v>-142.3446899462231</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3896483043887524</v>
+        <v>0.4087509879659054</v>
       </c>
       <c r="T83">
-        <v>7.941069385421534</v>
+        <v>8.382239906833842</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1094925223864464</v>
+        <v>0.1081572477231971</v>
       </c>
       <c r="W83">
-        <v>0.2099816632212759</v>
+        <v>0.2102965209868701</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4131793297601751</v>
+        <v>0.4081405574460267</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8374,22 +8374,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2460183250430965</v>
+        <v>0.2479183250430965</v>
       </c>
       <c r="C84">
-        <v>-1772.07492154797</v>
+        <v>-1841.840431356318</v>
       </c>
       <c r="D84">
-        <v>1005.116954111808</v>
+        <v>995.6684183968728</v>
       </c>
       <c r="E84">
-        <v>-350.0055336814148</v>
+        <v>-289.6885595880021</v>
       </c>
       <c r="F84">
-        <v>4945.991875659778</v>
+        <v>5006.308849753191</v>
       </c>
       <c r="G84">
         <v>2168.8</v>
@@ -8410,37 +8410,37 @@
         <v>476</v>
       </c>
       <c r="M84">
-        <v>1166.264884280576</v>
+        <v>1180.487626771803</v>
       </c>
       <c r="N84">
-        <v>-690.2648842805756</v>
+        <v>-704.4876267718025</v>
       </c>
       <c r="O84">
-        <v>-182.9201943343525</v>
+        <v>-186.6892210945277</v>
       </c>
       <c r="P84">
-        <v>-507.3446899462231</v>
+        <v>-517.7984056772748</v>
       </c>
       <c r="Q84">
-        <v>-142.3446899462231</v>
+        <v>-152.7984056772748</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4087509879659054</v>
+        <v>0.4301010460815469</v>
       </c>
       <c r="T84">
-        <v>8.382239906833842</v>
+        <v>8.875312842529951</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1081572477231971</v>
+        <v>0.1068541483530381</v>
       </c>
       <c r="W84">
-        <v>0.2102965209868701</v>
+        <v>0.2106037918183536</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4081405574460267</v>
+        <v>0.403223201332219</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8456,22 +8456,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2479183250430965</v>
+        <v>0.2498183250430965</v>
       </c>
       <c r="C85">
-        <v>-1841.840431356318</v>
+        <v>-1911.429954837411</v>
       </c>
       <c r="D85">
-        <v>995.6684183968728</v>
+        <v>986.3958690091916</v>
       </c>
       <c r="E85">
-        <v>-289.6885595880021</v>
+        <v>-229.3715854945904</v>
       </c>
       <c r="F85">
-        <v>5006.308849753191</v>
+        <v>5066.625823846603</v>
       </c>
       <c r="G85">
         <v>2168.8</v>
@@ -8492,37 +8492,37 @@
         <v>476</v>
       </c>
       <c r="M85">
-        <v>1180.487626771803</v>
+        <v>1194.710369263029</v>
       </c>
       <c r="N85">
-        <v>-704.4876267718025</v>
+        <v>-718.710369263029</v>
       </c>
       <c r="O85">
-        <v>-186.6892210945277</v>
+        <v>-190.4582478547027</v>
       </c>
       <c r="P85">
-        <v>-517.7984056772748</v>
+        <v>-528.2521214083263</v>
       </c>
       <c r="Q85">
-        <v>-152.7984056772748</v>
+        <v>-163.2521214083263</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4301010460815469</v>
+        <v>0.4541198614616437</v>
       </c>
       <c r="T85">
-        <v>8.875312842529951</v>
+        <v>9.430019895188076</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1068541483530381</v>
+        <v>0.105582075158359</v>
       </c>
       <c r="W85">
-        <v>0.2106037918183536</v>
+        <v>0.2109037466776589</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.403223201332219</v>
+        <v>0.3984229251258832</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8538,22 +8538,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2498183250430965</v>
+        <v>0.2517183250430964</v>
       </c>
       <c r="C86">
-        <v>-1911.429954837409</v>
+        <v>-1980.848363447275</v>
       </c>
       <c r="D86">
-        <v>986.3958690091921</v>
+        <v>977.2944344927387</v>
       </c>
       <c r="E86">
-        <v>-229.3715854945913</v>
+        <v>-169.0546114011795</v>
       </c>
       <c r="F86">
-        <v>5066.625823846602</v>
+        <v>5126.942797940013</v>
       </c>
       <c r="G86">
         <v>2168.8</v>
@@ -8574,37 +8574,37 @@
         <v>476</v>
       </c>
       <c r="M86">
-        <v>1194.710369263029</v>
+        <v>1208.933111754255</v>
       </c>
       <c r="N86">
-        <v>-718.7103692630287</v>
+        <v>-732.9331117542552</v>
       </c>
       <c r="O86">
-        <v>-190.4582478547026</v>
+        <v>-194.2272746148776</v>
       </c>
       <c r="P86">
-        <v>-528.252121408326</v>
+        <v>-538.7058371393775</v>
       </c>
       <c r="Q86">
-        <v>-163.252121408326</v>
+        <v>-173.7058371393775</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4541198614616433</v>
+        <v>0.4813411855590862</v>
       </c>
       <c r="T86">
-        <v>9.430019895188067</v>
+        <v>10.05868788820061</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1055820751583591</v>
+        <v>0.1043399330976725</v>
       </c>
       <c r="W86">
-        <v>0.2109037466776589</v>
+        <v>0.2111966437755688</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3984229251258832</v>
+        <v>0.3937355965949905</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8620,22 +8620,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2517183250430964</v>
+        <v>0.2536183250430964</v>
       </c>
       <c r="C87">
-        <v>-1980.848363447275</v>
+        <v>-2050.100350490826</v>
       </c>
       <c r="D87">
-        <v>977.2944344927387</v>
+        <v>968.3594215426</v>
       </c>
       <c r="E87">
-        <v>-169.0546114011795</v>
+        <v>-108.7376373077668</v>
       </c>
       <c r="F87">
-        <v>5126.942797940013</v>
+        <v>5187.259772033426</v>
       </c>
       <c r="G87">
         <v>2168.8</v>
@@ -8656,37 +8656,37 @@
         <v>476</v>
       </c>
       <c r="M87">
-        <v>1208.933111754255</v>
+        <v>1223.155854245482</v>
       </c>
       <c r="N87">
-        <v>-732.9331117542552</v>
+        <v>-747.155854245482</v>
       </c>
       <c r="O87">
-        <v>-194.2272746148776</v>
+        <v>-197.9963013750528</v>
       </c>
       <c r="P87">
-        <v>-538.7058371393775</v>
+        <v>-549.1595528704293</v>
       </c>
       <c r="Q87">
-        <v>-173.7058371393775</v>
+        <v>-184.1595528704293</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4813411855590862</v>
+        <v>0.5124512702418782</v>
       </c>
       <c r="T87">
-        <v>10.05868788820061</v>
+        <v>10.77716559450065</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1043399330976725</v>
+        <v>0.103126678061653</v>
       </c>
       <c r="W87">
-        <v>0.2111966437755688</v>
+        <v>0.2114827293130622</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3937355965949905</v>
+        <v>0.389157275704351</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8702,22 +8702,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2536183250430964</v>
+        <v>0.2555183250430965</v>
       </c>
       <c r="C88">
-        <v>-2050.100350490826</v>
+        <v>-2119.190439191904</v>
       </c>
       <c r="D88">
-        <v>968.3594215426</v>
+        <v>959.5863069349334</v>
       </c>
       <c r="E88">
-        <v>-108.7376373077668</v>
+        <v>-48.42066321435505</v>
       </c>
       <c r="F88">
-        <v>5187.259772033426</v>
+        <v>5247.576746126838</v>
       </c>
       <c r="G88">
         <v>2168.8</v>
@@ -8738,37 +8738,37 @@
         <v>476</v>
       </c>
       <c r="M88">
-        <v>1223.155854245482</v>
+        <v>1237.378596736708</v>
       </c>
       <c r="N88">
-        <v>-747.155854245482</v>
+        <v>-761.3785967367085</v>
       </c>
       <c r="O88">
-        <v>-197.9963013750528</v>
+        <v>-201.7653281352277</v>
       </c>
       <c r="P88">
-        <v>-549.1595528704293</v>
+        <v>-559.6132686014807</v>
       </c>
       <c r="Q88">
-        <v>-184.1595528704293</v>
+        <v>-194.6132686014807</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5124512702418782</v>
+        <v>0.5483475217989456</v>
       </c>
       <c r="T88">
-        <v>10.77716559450065</v>
+        <v>11.60617833253916</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.103126678061653</v>
+        <v>0.1019413139460018</v>
       </c>
       <c r="W88">
-        <v>0.2114827293130622</v>
+        <v>0.2117622381715328</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.389157275704351</v>
+        <v>0.3846842035698183</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8784,22 +8784,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2555183250430965</v>
+        <v>0.2574183250430965</v>
       </c>
       <c r="C89">
-        <v>-2119.190439191904</v>
+        <v>-2188.122990328585</v>
       </c>
       <c r="D89">
-        <v>959.5863069349334</v>
+        <v>950.9707298916642</v>
       </c>
       <c r="E89">
-        <v>-48.42066321435505</v>
+        <v>11.89631087905673</v>
       </c>
       <c r="F89">
-        <v>5247.576746126838</v>
+        <v>5307.89372022025</v>
       </c>
       <c r="G89">
         <v>2168.8</v>
@@ -8820,37 +8820,37 @@
         <v>476</v>
       </c>
       <c r="M89">
-        <v>1237.378596736708</v>
+        <v>1251.601339227935</v>
       </c>
       <c r="N89">
-        <v>-761.3785967367085</v>
+        <v>-775.6013392279349</v>
       </c>
       <c r="O89">
-        <v>-201.7653281352277</v>
+        <v>-205.5343548954027</v>
       </c>
       <c r="P89">
-        <v>-559.6132686014807</v>
+        <v>-570.0669843325321</v>
       </c>
       <c r="Q89">
-        <v>-194.6132686014807</v>
+        <v>-205.0669843325321</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5483475217989456</v>
+        <v>0.5902264819488579</v>
       </c>
       <c r="T89">
-        <v>11.60617833253916</v>
+        <v>12.57335986025076</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1019413139460018</v>
+        <v>0.1007828899238882</v>
       </c>
       <c r="W89">
-        <v>0.2117622381715328</v>
+        <v>0.2120353945559472</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3846842035698183</v>
+        <v>0.3803127921656158</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8866,22 +8866,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2574183250430965</v>
+        <v>0.2593183250430965</v>
       </c>
       <c r="C90">
-        <v>-2188.122990328585</v>
+        <v>-2256.902209460822</v>
       </c>
       <c r="D90">
-        <v>950.9707298916642</v>
+        <v>942.5084848528392</v>
       </c>
       <c r="E90">
-        <v>11.89631087905673</v>
+        <v>72.2132849724685</v>
       </c>
       <c r="F90">
-        <v>5307.89372022025</v>
+        <v>5368.210694313661</v>
       </c>
       <c r="G90">
         <v>2168.8</v>
@@ -8902,37 +8902,37 @@
         <v>476</v>
       </c>
       <c r="M90">
-        <v>1251.601339227935</v>
+        <v>1265.824081719161</v>
       </c>
       <c r="N90">
-        <v>-775.6013392279349</v>
+        <v>-789.8240817191613</v>
       </c>
       <c r="O90">
-        <v>-205.5343548954027</v>
+        <v>-209.3033816555778</v>
       </c>
       <c r="P90">
-        <v>-570.0669843325321</v>
+        <v>-580.5207000635835</v>
       </c>
       <c r="Q90">
-        <v>-205.0669843325321</v>
+        <v>-215.5207000635835</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5902264819488579</v>
+        <v>0.6397197984896631</v>
       </c>
       <c r="T90">
-        <v>12.57335986025076</v>
+        <v>13.71639257481901</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1007828899238882</v>
+        <v>0.09965049790227148</v>
       </c>
       <c r="W90">
-        <v>0.2120353945559472</v>
+        <v>0.2123024125946444</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3803127921656158</v>
+        <v>0.3760396147255527</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8948,22 +8948,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2593183250430965</v>
+        <v>0.2612183250430965</v>
       </c>
       <c r="C91">
-        <v>-2256.902209460822</v>
+        <v>-2325.532153775603</v>
       </c>
       <c r="D91">
-        <v>942.5084848528392</v>
+        <v>934.1955146314706</v>
       </c>
       <c r="E91">
-        <v>72.2132849724685</v>
+        <v>132.5302590658803</v>
       </c>
       <c r="F91">
-        <v>5368.210694313661</v>
+        <v>5428.527668407073</v>
       </c>
       <c r="G91">
         <v>2168.8</v>
@@ -8984,37 +8984,37 @@
         <v>476</v>
       </c>
       <c r="M91">
-        <v>1265.824081719161</v>
+        <v>1280.046824210388</v>
       </c>
       <c r="N91">
-        <v>-789.8240817191613</v>
+        <v>-804.046824210388</v>
       </c>
       <c r="O91">
-        <v>-209.3033816555778</v>
+        <v>-213.0724084157528</v>
       </c>
       <c r="P91">
-        <v>-580.5207000635835</v>
+        <v>-590.9744157946352</v>
       </c>
       <c r="Q91">
-        <v>-215.5207000635835</v>
+        <v>-225.9744157946352</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6397197984896631</v>
+        <v>0.6991117783386296</v>
       </c>
       <c r="T91">
-        <v>13.71639257481901</v>
+        <v>15.08803183230092</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09965049790227148</v>
+        <v>0.09854327014780179</v>
       </c>
       <c r="W91">
-        <v>0.2123024125946444</v>
+        <v>0.2125634968991484</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3760396147255527</v>
+        <v>0.3718613967841576</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9030,22 +9030,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2612183250430965</v>
+        <v>0.2631183250430965</v>
       </c>
       <c r="C92">
-        <v>-2325.532153775603</v>
+        <v>-2394.016738573026</v>
       </c>
       <c r="D92">
-        <v>934.1955146314706</v>
+        <v>926.0279039274595</v>
       </c>
       <c r="E92">
-        <v>132.5302590658803</v>
+        <v>192.847233159293</v>
       </c>
       <c r="F92">
-        <v>5428.527668407073</v>
+        <v>5488.844642500486</v>
       </c>
       <c r="G92">
         <v>2168.8</v>
@@ -9066,37 +9066,37 @@
         <v>476</v>
       </c>
       <c r="M92">
-        <v>1280.046824210388</v>
+        <v>1294.269566701615</v>
       </c>
       <c r="N92">
-        <v>-804.046824210388</v>
+        <v>-818.2695667016146</v>
       </c>
       <c r="O92">
-        <v>-213.0724084157528</v>
+        <v>-216.8414351759279</v>
       </c>
       <c r="P92">
-        <v>-590.9744157946352</v>
+        <v>-601.4281315256867</v>
       </c>
       <c r="Q92">
-        <v>-225.9744157946352</v>
+        <v>-236.4281315256867</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6991117783386296</v>
+        <v>0.7717019759318107</v>
       </c>
       <c r="T92">
-        <v>15.08803183230092</v>
+        <v>16.76447981366768</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09854327014780179</v>
+        <v>0.09746037706925451</v>
       </c>
       <c r="W92">
-        <v>0.2125634968991484</v>
+        <v>0.2128188430870698</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3718613967841576</v>
+        <v>0.3677750078085076</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9112,22 +9112,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2631183250430965</v>
+        <v>0.2650183250430965</v>
       </c>
       <c r="C93">
-        <v>-2394.016738573026</v>
+        <v>-2462.359743415082</v>
       </c>
       <c r="D93">
-        <v>926.0279039274595</v>
+        <v>918.0018731788151</v>
       </c>
       <c r="E93">
-        <v>192.847233159293</v>
+        <v>253.1642072527047</v>
       </c>
       <c r="F93">
-        <v>5488.844642500486</v>
+        <v>5549.161616593898</v>
       </c>
       <c r="G93">
         <v>2168.8</v>
@@ -9148,37 +9148,37 @@
         <v>476</v>
       </c>
       <c r="M93">
-        <v>1294.269566701615</v>
+        <v>1308.492309192841</v>
       </c>
       <c r="N93">
-        <v>-818.2695667016146</v>
+        <v>-832.492309192841</v>
       </c>
       <c r="O93">
-        <v>-216.8414351759279</v>
+        <v>-220.6104619361029</v>
       </c>
       <c r="P93">
-        <v>-601.4281315256867</v>
+        <v>-611.8818472567382</v>
       </c>
       <c r="Q93">
-        <v>-236.4281315256867</v>
+        <v>-246.8818472567382</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7717019759318107</v>
+        <v>0.8624397229232873</v>
       </c>
       <c r="T93">
-        <v>16.76447981366768</v>
+        <v>18.86003979037615</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09746037706925451</v>
+        <v>0.0964010251445887</v>
       </c>
       <c r="W93">
-        <v>0.2128188430870698</v>
+        <v>0.213068638270906</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3677750078085076</v>
+        <v>0.3637774533758064</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9194,22 +9194,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2650183250430965</v>
+        <v>0.2669183250430965</v>
       </c>
       <c r="C94">
-        <v>-2462.359743415082</v>
+        <v>-2530.564817957427</v>
       </c>
       <c r="D94">
-        <v>918.0018731788151</v>
+        <v>910.1137727298822</v>
       </c>
       <c r="E94">
-        <v>253.1642072527047</v>
+        <v>313.4811813461165</v>
       </c>
       <c r="F94">
-        <v>5549.161616593898</v>
+        <v>5609.478590687309</v>
       </c>
       <c r="G94">
         <v>2168.8</v>
@@ -9230,37 +9230,37 @@
         <v>476</v>
       </c>
       <c r="M94">
-        <v>1308.492309192841</v>
+        <v>1322.715051684068</v>
       </c>
       <c r="N94">
-        <v>-832.492309192841</v>
+        <v>-846.7150516840677</v>
       </c>
       <c r="O94">
-        <v>-220.6104619361029</v>
+        <v>-224.3794886962779</v>
       </c>
       <c r="P94">
-        <v>-611.8818472567382</v>
+        <v>-622.3355629877898</v>
       </c>
       <c r="Q94">
-        <v>-246.8818472567382</v>
+        <v>-257.3355629877898</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8624397229232873</v>
+        <v>0.9791025404837571</v>
       </c>
       <c r="T94">
-        <v>18.86003979037615</v>
+        <v>21.55433118900132</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0964010251445887</v>
+        <v>0.09536445498174365</v>
       </c>
       <c r="W94">
-        <v>0.213068638270906</v>
+        <v>0.2133130615153049</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3637774533758064</v>
+        <v>0.3598658678556365</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9276,22 +9276,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2669183250430965</v>
+        <v>0.2688183250430965</v>
       </c>
       <c r="C95">
-        <v>-2530.564817957427</v>
+        <v>-2598.635487483054</v>
       </c>
       <c r="D95">
-        <v>910.1137727298822</v>
+        <v>902.3600772976675</v>
       </c>
       <c r="E95">
-        <v>313.4811813461165</v>
+        <v>373.7981554395283</v>
       </c>
       <c r="F95">
-        <v>5609.478590687309</v>
+        <v>5669.795564780721</v>
       </c>
       <c r="G95">
         <v>2168.8</v>
@@ -9312,37 +9312,37 @@
         <v>476</v>
       </c>
       <c r="M95">
-        <v>1322.715051684068</v>
+        <v>1336.937794175294</v>
       </c>
       <c r="N95">
-        <v>-846.7150516840677</v>
+        <v>-860.9377941752941</v>
       </c>
       <c r="O95">
-        <v>-224.3794886962779</v>
+        <v>-228.148515456453</v>
       </c>
       <c r="P95">
-        <v>-622.3355629877898</v>
+        <v>-632.7892787188412</v>
       </c>
       <c r="Q95">
-        <v>-257.3355629877898</v>
+        <v>-267.7892787188412</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9791025404837571</v>
+        <v>1.134652963897717</v>
       </c>
       <c r="T95">
-        <v>21.55433118900132</v>
+        <v>25.14671972050154</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09536445498174365</v>
+        <v>0.09434993950321446</v>
       </c>
       <c r="W95">
-        <v>0.2133130615153049</v>
+        <v>0.213552284265142</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3598658678556365</v>
+        <v>0.3560375075592999</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9358,22 +9358,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2688183250430965</v>
+        <v>0.2707183250430965</v>
       </c>
       <c r="C96">
-        <v>-2598.635487483054</v>
+        <v>-2666.575158155489</v>
       </c>
       <c r="D96">
-        <v>902.3600772976675</v>
+        <v>894.7373807186449</v>
       </c>
       <c r="E96">
-        <v>373.7981554395283</v>
+        <v>434.115129532941</v>
       </c>
       <c r="F96">
-        <v>5669.795564780721</v>
+        <v>5730.112538874134</v>
       </c>
       <c r="G96">
         <v>2168.8</v>
@@ -9394,37 +9394,37 @@
         <v>476</v>
       </c>
       <c r="M96">
-        <v>1336.937794175294</v>
+        <v>1351.160536666521</v>
       </c>
       <c r="N96">
-        <v>-860.9377941752941</v>
+        <v>-875.1605366665208</v>
       </c>
       <c r="O96">
-        <v>-228.148515456453</v>
+        <v>-231.917542216628</v>
       </c>
       <c r="P96">
-        <v>-632.7892787188412</v>
+        <v>-643.2429944498928</v>
       </c>
       <c r="Q96">
-        <v>-267.7892787188412</v>
+        <v>-278.2429944498928</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.134652963897717</v>
+        <v>1.352423556677261</v>
       </c>
       <c r="T96">
-        <v>25.14671972050154</v>
+        <v>30.17606366460187</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09434993950321446</v>
+        <v>0.09335678224528589</v>
       </c>
       <c r="W96">
-        <v>0.213552284265142</v>
+        <v>0.2137864707465616</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3560375075592999</v>
+        <v>0.3522897443218336</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9440,22 +9440,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2707183250430965</v>
+        <v>0.2726183250430965</v>
       </c>
       <c r="C97">
-        <v>-2666.575158155489</v>
+        <v>-2734.387122007962</v>
       </c>
       <c r="D97">
-        <v>894.7373807186449</v>
+        <v>887.2423909595838</v>
       </c>
       <c r="E97">
-        <v>434.115129532941</v>
+        <v>494.4321036263527</v>
       </c>
       <c r="F97">
-        <v>5730.112538874134</v>
+        <v>5790.429512967546</v>
       </c>
       <c r="G97">
         <v>2168.8</v>
@@ -9476,37 +9476,37 @@
         <v>476</v>
       </c>
       <c r="M97">
-        <v>1351.160536666521</v>
+        <v>1365.383279157747</v>
       </c>
       <c r="N97">
-        <v>-875.1605366665208</v>
+        <v>-889.3832791577472</v>
       </c>
       <c r="O97">
-        <v>-231.917542216628</v>
+        <v>-235.686568976803</v>
       </c>
       <c r="P97">
-        <v>-643.2429944498928</v>
+        <v>-653.6967101809441</v>
       </c>
       <c r="Q97">
-        <v>-278.2429944498928</v>
+        <v>-288.6967101809441</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.352423556677261</v>
+        <v>1.679079445846577</v>
       </c>
       <c r="T97">
-        <v>30.17606366460187</v>
+        <v>37.72007958075235</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09335678224528589</v>
+        <v>0.09238431576356416</v>
       </c>
       <c r="W97">
-        <v>0.2137864707465616</v>
+        <v>0.2140157783429516</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3522897443218336</v>
+        <v>0.3486200594851478</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9522,22 +9522,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2726183250430965</v>
+        <v>0.2745183250430965</v>
       </c>
       <c r="C98">
-        <v>-2734.387122007961</v>
+        <v>-2802.074561683899</v>
       </c>
       <c r="D98">
-        <v>887.2423909595838</v>
+        <v>879.8719253770572</v>
       </c>
       <c r="E98">
-        <v>494.4321036263518</v>
+        <v>554.7490777197636</v>
       </c>
       <c r="F98">
-        <v>5790.429512967545</v>
+        <v>5850.746487060956</v>
       </c>
       <c r="G98">
         <v>2168.8</v>
@@ -9558,37 +9558,37 @@
         <v>476</v>
       </c>
       <c r="M98">
-        <v>1365.383279157747</v>
+        <v>1379.606021648974</v>
       </c>
       <c r="N98">
-        <v>-889.3832791577472</v>
+        <v>-903.6060216489736</v>
       </c>
       <c r="O98">
-        <v>-235.686568976803</v>
+        <v>-239.455595736978</v>
       </c>
       <c r="P98">
-        <v>-653.6967101809441</v>
+        <v>-664.1504259119956</v>
       </c>
       <c r="Q98">
-        <v>-288.6967101809441</v>
+        <v>-299.1504259119956</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.679079445846572</v>
+        <v>2.22350592779543</v>
       </c>
       <c r="T98">
-        <v>37.72007958075225</v>
+        <v>50.293439441003</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09238431576356416</v>
+        <v>0.09143190013713567</v>
       </c>
       <c r="W98">
-        <v>0.2140157783429516</v>
+        <v>0.2142403579476634</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3486200594851478</v>
+        <v>0.3450260382533422</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9604,22 +9604,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2745183250430965</v>
+        <v>0.2764183250430965</v>
       </c>
       <c r="C99">
-        <v>-2802.074561683899</v>
+        <v>-2869.640554943087</v>
       </c>
       <c r="D99">
-        <v>879.8719253770572</v>
+        <v>872.622906211282</v>
       </c>
       <c r="E99">
-        <v>554.7490777197636</v>
+        <v>615.0660518131763</v>
       </c>
       <c r="F99">
-        <v>5850.746487060956</v>
+        <v>5911.063461154369</v>
       </c>
       <c r="G99">
         <v>2168.8</v>
@@ -9640,37 +9640,37 @@
         <v>476</v>
       </c>
       <c r="M99">
-        <v>1379.606021648974</v>
+        <v>1393.8287641402</v>
       </c>
       <c r="N99">
-        <v>-903.6060216489736</v>
+        <v>-917.8287641402003</v>
       </c>
       <c r="O99">
-        <v>-239.455595736978</v>
+        <v>-243.2246224971531</v>
       </c>
       <c r="P99">
-        <v>-664.1504259119956</v>
+        <v>-674.6041416430472</v>
       </c>
       <c r="Q99">
-        <v>-299.1504259119956</v>
+        <v>-309.6041416430472</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.22350592779543</v>
+        <v>3.312358891693144</v>
       </c>
       <c r="T99">
-        <v>50.293439441003</v>
+        <v>75.4401591615045</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09143190013713567</v>
+        <v>0.09049892156430776</v>
       </c>
       <c r="W99">
-        <v>0.2142403579476634</v>
+        <v>0.2144603542951362</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3450260382533422</v>
+        <v>0.3415053643936141</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9686,22 +9686,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2764183250430965</v>
+        <v>0.2783183250430964</v>
       </c>
       <c r="C100">
-        <v>-2869.640554943087</v>
+        <v>-2937.088078946895</v>
       </c>
       <c r="D100">
-        <v>872.622906211282</v>
+        <v>865.4923563008863</v>
       </c>
       <c r="E100">
-        <v>615.0660518131763</v>
+        <v>675.383025906588</v>
       </c>
       <c r="F100">
-        <v>5911.063461154369</v>
+        <v>5971.380435247781</v>
       </c>
       <c r="G100">
         <v>2168.8</v>
@@ -9722,37 +9722,37 @@
         <v>476</v>
       </c>
       <c r="M100">
-        <v>1393.8287641402</v>
+        <v>1408.051506631427</v>
       </c>
       <c r="N100">
-        <v>-917.8287641402003</v>
+        <v>-932.0515066314267</v>
       </c>
       <c r="O100">
-        <v>-243.2246224971531</v>
+        <v>-246.9936492573281</v>
       </c>
       <c r="P100">
-        <v>-674.6041416430472</v>
+        <v>-685.0578573740986</v>
       </c>
       <c r="Q100">
-        <v>-309.6041416430472</v>
+        <v>-320.0578573740986</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.312358891693144</v>
+        <v>6.578917783386289</v>
       </c>
       <c r="T100">
-        <v>75.4401591615045</v>
+        <v>150.880318323009</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09049892156430776</v>
+        <v>0.08958479104345618</v>
       </c>
       <c r="W100">
-        <v>0.2144603542951362</v>
+        <v>0.214675906271953</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9760,91 +9760,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3415053643936141</v>
+        <v>0.3380558152583252</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2783183250430964</v>
-      </c>
-      <c r="C101">
-        <v>-2937.088078946895</v>
-      </c>
-      <c r="D101">
-        <v>865.4923563008863</v>
-      </c>
-      <c r="E101">
-        <v>675.383025906588</v>
-      </c>
-      <c r="F101">
-        <v>5971.380435247781</v>
-      </c>
-      <c r="G101">
-        <v>2168.8</v>
-      </c>
-      <c r="H101">
-        <v>735.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>841</v>
-      </c>
-      <c r="K101">
-        <v>365</v>
-      </c>
-      <c r="L101">
-        <v>476</v>
-      </c>
-      <c r="M101">
-        <v>1408.051506631427</v>
-      </c>
-      <c r="N101">
-        <v>-932.0515066314267</v>
-      </c>
-      <c r="O101">
-        <v>-246.9936492573281</v>
-      </c>
-      <c r="P101">
-        <v>-685.0578573740986</v>
-      </c>
-      <c r="Q101">
-        <v>-320.0578573740986</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.578917783386289</v>
-      </c>
-      <c r="T101">
-        <v>150.880318323009</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08958479104345618</v>
-      </c>
-      <c r="W101">
-        <v>0.214675906271953</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3380558152583252</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
